--- a/data/monthly/【2025年11月】月次数値.xlsx
+++ b/data/monthly/【2025年11月】月次数値.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1129" uniqueCount="213">
   <si>
     <t>レポート開始日</t>
   </si>
@@ -328,6 +328,375 @@
   </si>
   <si>
     <t>COCORO エステサロン</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【Dining Bar Lien】...</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 📍町寿司いちもんめ｜福井市大手...</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🌸【女性クリニック ラポール】🌸
+すべての世代の女性に、安心と寄り添いを。...</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 📍Wild Crepes - ワイルドクレープス
+安い！旨い！多い！🎉...</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍸【bar moon walk 三条木屋町店】🌙...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍶【駕町 とくさ】熊本・花畑町駅 徒歩5分...</t>
+  </si>
+  <si>
+    <t>炭焼　猿一</t>
+  </si>
+  <si>
+    <t>2026-01-15</t>
+  </si>
+  <si>
+    <t>島田屋　東苗穂店</t>
+  </si>
+  <si>
+    <t>居ZAKKU　CHENOWA</t>
+  </si>
+  <si>
+    <t>三千段の民宿　幸登里</t>
+  </si>
+  <si>
+    <t>てんぐ屋</t>
+  </si>
+  <si>
+    <t>炭火焼肉友丸</t>
+  </si>
+  <si>
+    <t>旬彩屋　笑味</t>
+  </si>
+  <si>
+    <t>有限会社　大嶋_うまか喰い処 祇園 大しま</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【海鮮と肉料理 ほっかい酒房】🍣🍢✨
+すすきの駅から徒歩3分🚶‍♂️...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【せがわ歯科クリニック】です🦷✨...</t>
+  </si>
+  <si>
+    <t>2026-08-24</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【ORINAS】です🍽️✨...</t>
+  </si>
+  <si>
+    <t>2026-08-31</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【CasualClub青】です🎤✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【Mix Bar Blo】です🍸✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【はんすう】です🍦✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 新潟県長岡市に佇むカフェ『樹林館』🌳☕️...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 「新潟県長岡市に佇むカフェ『樹林館』🌳☕️...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍴肴家 信清🍷...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 家系ラーメン武将家　浅草店
+10月5日にオープンした『家系らーめん...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 「SEA DROP Roast...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍽️【特別な日のご褒美に】...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 和牛焼肉としお
+🥩和牛焼肉の新境地へ— 🥩...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍜日々“育てる”一杯、ここにあり🔥...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍷✨クオリティ高×価格安×lowkeyな接客✨🍴...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: ✨2024年9月20日 NEW OPEN✨
+Hairsalon...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【Meibuキッズ空手教室】
+＼2〜3歳のお子さまも大歓迎👶✨／...</t>
+  </si>
+  <si>
+    <t>2026-01-02</t>
+  </si>
+  <si>
+    <t>Instagram投稿: インプラント治療なら「上志津中央歯科」🌟...</t>
+  </si>
+  <si>
+    <t>recently_completed</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 中洲にあるミュージックカラオケバー！Food持ち込み可🍴🎶...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🔥【香り豊かな炭火焼と多彩な日本酒が楽しめる！】🔥...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: んにちは！【Mont Blanc】です🍸✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🌟SUNRISEガールズバー｜豊田市山之手🌟...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍷 株式会社 TechVoice・FRETTA 🍸
+✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 📢 株式会社 TechVoice・FRETTA スタッフ募集中！ 🍸
+✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🏡☕canurip Cafe☕🏡
+茨木に佇む韓国風古民家カフェღ...</t>
+  </si>
+  <si>
+    <t>2026-09-27</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍻 鉄板居酒屋こぐま 🔥
+🏡 アットホームな空間で、心もお腹も大満足！...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 至福のひとときを、すすきの 蟹一 で。
+✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍶 合同会社 大和・北海道の幸とお酒 たかふじ 🐟
+✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: ✨ 天ぷら むらやま｜吉祥寺 ✨
+ゆったりとした カウンター席...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 遠心太助 – 新発想の洗浄ツールで塗装コスト削減！ 🌍
+🔹...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍷 pikku onni 🍽️
+🐟 北海道の海の恵み ×...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🥩 焼肉処 縁結び｜鮮度抜群の極上焼肉 🥩...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🎤 カラオケサーカス 調布店 🎪✨
+東京・調布市の音楽オアシス！🌆🎶...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🌟大林歯科医院｜千葉県美浜区幕張西🌟...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🌟栄駅から徒歩2分の歯医者【日生歯科診療所】🌟...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🌟府中市の歯医者【たかすぎ歯科クリニック】🌟...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🌟かわらもと歯科｜大阪市・吹田市🌟...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍻【リーズナブルにたくさん食べたいなら「居酒屋一（ichi）」】🍻...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: ✨【国分町に新しい刺激を！】✨
+「Extreme Bar...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🌻季節の食材を使った心温まるお料理とお酒🌻...</t>
+  </si>
+  <si>
+    <t>2026-09-29</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🌟【焼鳥の真髄、ここにあり】🌟
+「焼鳥酒場...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🌙【川越の夜をおしゃれに楽しむならここ！】🌙
+「AMUSEMENT Bar...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🐾✨ Heart Dog ✨🐶
+ドッグカフェ 庵（いおり） OPEN！...</t>
+  </si>
+  <si>
+    <t>2026-04-01</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【髙橋歯科】
+“噛み合わせ”から整える、お口とカラダのトータルケア🪥...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍽️【リラックスしたひとときを「HIDEOUT」で】🍷...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🔥 ホルモン 焼肉 楽丸...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🥩✨ステーキTaka✨🥩...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🔥 炭火焼とり 隼...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍷 えびすバル –自家製ローストビーフと自然派ワインのマリアージュを🥩...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: ✨ 高岡市のバー【NUTS】へようこそ！🍹...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍽️ おるたなキッチン – カフェみたいな定食屋で心ほっこりごはん時間☕🍱...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: LEAP SPORTS GYMで、一緒に成長しよう！💪🔥
+🏋️‍♂️...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🌴 Manly Australian Cafe ＆ Bar 🇦🇺
+📍...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🦌🦪 鹿肉＆オイスターバル SLOW...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🎤✨ snack &amp; karaoke bar Belle 🍸🎶...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍶✨ 居酒屋1484（イシバシ） 🍽️🎣
+📍 大宮駅東口から徒歩すぐ！
+✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍁 旬彩和食よし田 🍁
+📍 つくば市の本格和食店
+✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🌿 HATASU 🌱
+植物と暮らそう。
+何気ない日常に 緑...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍷 肉とワインのイタリアン酒場 more 前橋店 🥩
+📍...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍷 肉とワインのイタリアン酒場 more 高崎店 🥩
+📍...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【Meibuキッズ空手教室】
+＼ドキドキ💓はじめてのスポーツ体験！／...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【すし嘉まさ】🍣✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【すし嘉まさ】新しい仲間を募集しています！🍣✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【鮨一花】🍣✨
+豊水すすきの駅から徒歩1分🚶‍♂️🎶...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🥢 中華バル Chiry - チャイリー 🍻
+📍...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🎉【スナックバー Reina 求人募集】🎉...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🥩 焼肉 からし亭 東高円寺店 🍽...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🥩 焼肉 からし亭 新高円寺店 🍽...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🥢【とんかつ樹｜こだわり抜いた食材と空間で味わう極上のひととき】🥢...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🥩 焼肉 からし亭 経堂店 🔥
+〜...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🥩 炭火焼肉 からし亭 八戸店 🥢
+〜...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🥩 焼肉 からし亭 三沢店 🍚✨
+〜...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【Meibuキッズ空手教室】🥋✨...</t>
+  </si>
+  <si>
+    <t>2026-01-01</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🌟 2024年9月、津田沼にNEW OPEN！🌟...</t>
+  </si>
+  <si>
+    <t>2026-11-30</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🦷【地域密着！いつでも安心のかかりつけ歯科】...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🦷【日野市で予防歯科なら！】...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: ✨【透明感のある白い歯を目指して】✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🎵✨ BAR EIT8で特別なひと時を✨🎵...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: ✨【求人募集】✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🦷【船橋市で理想の口元へ】🦷
+医療法人社団哲の子会...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍶居酒屋ちるとSake 三軒茶屋店✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🦷✨ チロル歯科 ✨🦷...</t>
   </si>
 </sst>
 </file>
@@ -677,7 +1046,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y42"/>
+  <dimension ref="A1:Y142"/>
   <sheetFormatPr defaultColWidth="20" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.3">
@@ -3615,6 +3984,6866 @@
       </c>
       <c r="Y42">
         <v>48.796875</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>25</v>
+      </c>
+      <c r="B43" t="s">
+        <v>26</v>
+      </c>
+      <c r="C43" t="s">
+        <v>103</v>
+      </c>
+      <c r="D43" t="s">
+        <v>68</v>
+      </c>
+      <c r="E43" t="s">
+        <v>29</v>
+      </c>
+      <c r="F43">
+        <v>128</v>
+      </c>
+      <c r="G43" t="s">
+        <v>39</v>
+      </c>
+      <c r="H43">
+        <v>5219</v>
+      </c>
+      <c r="I43">
+        <v>1.436674</v>
+      </c>
+      <c r="J43">
+        <v>37.59375</v>
+      </c>
+      <c r="K43">
+        <v>160</v>
+      </c>
+      <c r="L43" t="s">
+        <v>30</v>
+      </c>
+      <c r="M43">
+        <v>4812</v>
+      </c>
+      <c r="N43" t="s">
+        <v>104</v>
+      </c>
+      <c r="O43">
+        <v>7498</v>
+      </c>
+      <c r="P43">
+        <v>641.77113899999995</v>
+      </c>
+      <c r="Q43">
+        <v>128</v>
+      </c>
+      <c r="S43">
+        <v>37.59375</v>
+      </c>
+      <c r="T43">
+        <v>1.707122</v>
+      </c>
+      <c r="U43">
+        <v>190</v>
+      </c>
+      <c r="V43">
+        <v>2.5340090000000002</v>
+      </c>
+      <c r="W43">
+        <v>25.326315999999998</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>25</v>
+      </c>
+      <c r="B44" t="s">
+        <v>26</v>
+      </c>
+      <c r="C44" t="s">
+        <v>105</v>
+      </c>
+      <c r="D44" t="s">
+        <v>28</v>
+      </c>
+      <c r="E44" t="s">
+        <v>29</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>160</v>
+      </c>
+      <c r="L44" t="s">
+        <v>30</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44" t="s">
+        <v>106</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>0</v>
+      </c>
+      <c r="U44">
+        <v>0</v>
+      </c>
+      <c r="V44">
+        <v>0</v>
+      </c>
+      <c r="W44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>25</v>
+      </c>
+      <c r="B45" t="s">
+        <v>26</v>
+      </c>
+      <c r="C45" t="s">
+        <v>107</v>
+      </c>
+      <c r="D45" t="s">
+        <v>68</v>
+      </c>
+      <c r="E45" t="s">
+        <v>29</v>
+      </c>
+      <c r="F45">
+        <v>88</v>
+      </c>
+      <c r="G45" t="s">
+        <v>39</v>
+      </c>
+      <c r="H45">
+        <v>2637</v>
+      </c>
+      <c r="I45">
+        <v>1.5271140000000001</v>
+      </c>
+      <c r="J45">
+        <v>54.69318182</v>
+      </c>
+      <c r="K45">
+        <v>160</v>
+      </c>
+      <c r="L45" t="s">
+        <v>30</v>
+      </c>
+      <c r="M45">
+        <v>4813</v>
+      </c>
+      <c r="N45" t="s">
+        <v>108</v>
+      </c>
+      <c r="O45">
+        <v>4027</v>
+      </c>
+      <c r="P45">
+        <v>1195.1825180000001</v>
+      </c>
+      <c r="Q45">
+        <v>88</v>
+      </c>
+      <c r="S45">
+        <v>54.693182</v>
+      </c>
+      <c r="T45">
+        <v>2.1852499999999999</v>
+      </c>
+      <c r="U45">
+        <v>102</v>
+      </c>
+      <c r="V45">
+        <v>2.5329030000000001</v>
+      </c>
+      <c r="W45">
+        <v>47.186275000000002</v>
+      </c>
+    </row>
+    <row r="46" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>25</v>
+      </c>
+      <c r="B46" t="s">
+        <v>26</v>
+      </c>
+      <c r="C46" t="s">
+        <v>109</v>
+      </c>
+      <c r="D46" t="s">
+        <v>68</v>
+      </c>
+      <c r="E46" t="s">
+        <v>29</v>
+      </c>
+      <c r="F46">
+        <v>194</v>
+      </c>
+      <c r="G46" t="s">
+        <v>39</v>
+      </c>
+      <c r="H46">
+        <v>4664</v>
+      </c>
+      <c r="I46">
+        <v>1.404374</v>
+      </c>
+      <c r="J46">
+        <v>24.793814430000001</v>
+      </c>
+      <c r="K46">
+        <v>160</v>
+      </c>
+      <c r="L46" t="s">
+        <v>30</v>
+      </c>
+      <c r="M46">
+        <v>4810</v>
+      </c>
+      <c r="N46" t="s">
+        <v>110</v>
+      </c>
+      <c r="O46">
+        <v>6550</v>
+      </c>
+      <c r="P46">
+        <v>734.35114499999997</v>
+      </c>
+      <c r="Q46">
+        <v>194</v>
+      </c>
+      <c r="S46">
+        <v>24.793814000000001</v>
+      </c>
+      <c r="T46">
+        <v>2.9618319999999998</v>
+      </c>
+      <c r="U46">
+        <v>235</v>
+      </c>
+      <c r="V46">
+        <v>3.5877859999999999</v>
+      </c>
+      <c r="W46">
+        <v>20.468084999999999</v>
+      </c>
+    </row>
+    <row r="47" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>25</v>
+      </c>
+      <c r="B47" t="s">
+        <v>26</v>
+      </c>
+      <c r="C47" t="s">
+        <v>111</v>
+      </c>
+      <c r="D47" t="s">
+        <v>68</v>
+      </c>
+      <c r="E47" t="s">
+        <v>29</v>
+      </c>
+      <c r="F47">
+        <v>65</v>
+      </c>
+      <c r="G47" t="s">
+        <v>39</v>
+      </c>
+      <c r="H47">
+        <v>1374</v>
+      </c>
+      <c r="I47">
+        <v>1.2612810000000001</v>
+      </c>
+      <c r="J47">
+        <v>73.369230770000001</v>
+      </c>
+      <c r="K47">
+        <v>160</v>
+      </c>
+      <c r="L47" t="s">
+        <v>30</v>
+      </c>
+      <c r="M47">
+        <v>4769</v>
+      </c>
+      <c r="N47" t="s">
+        <v>110</v>
+      </c>
+      <c r="O47">
+        <v>1733</v>
+      </c>
+      <c r="P47">
+        <v>2751.8753609999999</v>
+      </c>
+      <c r="Q47">
+        <v>65</v>
+      </c>
+      <c r="S47">
+        <v>73.369230999999999</v>
+      </c>
+      <c r="T47">
+        <v>3.750721</v>
+      </c>
+      <c r="U47">
+        <v>72</v>
+      </c>
+      <c r="V47">
+        <v>4.1546450000000004</v>
+      </c>
+      <c r="W47">
+        <v>66.236110999999994</v>
+      </c>
+    </row>
+    <row r="48" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>25</v>
+      </c>
+      <c r="B48" t="s">
+        <v>26</v>
+      </c>
+      <c r="C48" t="s">
+        <v>112</v>
+      </c>
+      <c r="D48" t="s">
+        <v>68</v>
+      </c>
+      <c r="E48" t="s">
+        <v>29</v>
+      </c>
+      <c r="F48">
+        <v>250</v>
+      </c>
+      <c r="G48" t="s">
+        <v>39</v>
+      </c>
+      <c r="H48">
+        <v>3329</v>
+      </c>
+      <c r="I48">
+        <v>1.642836</v>
+      </c>
+      <c r="J48">
+        <v>19.263999999999999</v>
+      </c>
+      <c r="K48">
+        <v>160</v>
+      </c>
+      <c r="L48" t="s">
+        <v>30</v>
+      </c>
+      <c r="M48">
+        <v>4816</v>
+      </c>
+      <c r="N48" t="s">
+        <v>110</v>
+      </c>
+      <c r="O48">
+        <v>5469</v>
+      </c>
+      <c r="P48">
+        <v>880.59974399999999</v>
+      </c>
+      <c r="Q48">
+        <v>250</v>
+      </c>
+      <c r="S48">
+        <v>19.263999999999999</v>
+      </c>
+      <c r="T48">
+        <v>4.5712200000000003</v>
+      </c>
+      <c r="U48">
+        <v>297</v>
+      </c>
+      <c r="V48">
+        <v>5.4306089999999996</v>
+      </c>
+      <c r="W48">
+        <v>16.215488000000001</v>
+      </c>
+    </row>
+    <row r="49" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>25</v>
+      </c>
+      <c r="B49" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" t="s">
+        <v>113</v>
+      </c>
+      <c r="D49" t="s">
+        <v>68</v>
+      </c>
+      <c r="E49" t="s">
+        <v>29</v>
+      </c>
+      <c r="F49">
+        <v>244</v>
+      </c>
+      <c r="G49" t="s">
+        <v>39</v>
+      </c>
+      <c r="H49">
+        <v>4816</v>
+      </c>
+      <c r="I49">
+        <v>1.419643</v>
+      </c>
+      <c r="J49">
+        <v>20.143442619999998</v>
+      </c>
+      <c r="K49" t="s">
+        <v>34</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <v>4915</v>
+      </c>
+      <c r="N49" t="s">
+        <v>114</v>
+      </c>
+      <c r="O49">
+        <v>6837</v>
+      </c>
+      <c r="P49">
+        <v>718.88255100000003</v>
+      </c>
+      <c r="Q49">
+        <v>244</v>
+      </c>
+      <c r="S49">
+        <v>20.143443000000001</v>
+      </c>
+      <c r="T49">
+        <v>3.5688170000000001</v>
+      </c>
+      <c r="U49">
+        <v>259</v>
+      </c>
+      <c r="V49">
+        <v>3.788211</v>
+      </c>
+      <c r="W49">
+        <v>18.976834</v>
+      </c>
+    </row>
+    <row r="50" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>25</v>
+      </c>
+      <c r="B50" t="s">
+        <v>26</v>
+      </c>
+      <c r="C50" t="s">
+        <v>115</v>
+      </c>
+      <c r="D50" t="s">
+        <v>68</v>
+      </c>
+      <c r="E50" t="s">
+        <v>29</v>
+      </c>
+      <c r="F50">
+        <v>266</v>
+      </c>
+      <c r="G50" t="s">
+        <v>39</v>
+      </c>
+      <c r="H50">
+        <v>6354</v>
+      </c>
+      <c r="I50">
+        <v>1.312087</v>
+      </c>
+      <c r="J50">
+        <v>18.89097744</v>
+      </c>
+      <c r="K50" t="s">
+        <v>34</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50">
+        <v>5025</v>
+      </c>
+      <c r="N50" t="s">
+        <v>114</v>
+      </c>
+      <c r="O50">
+        <v>8337</v>
+      </c>
+      <c r="P50">
+        <v>602.73479699999996</v>
+      </c>
+      <c r="Q50">
+        <v>266</v>
+      </c>
+      <c r="S50">
+        <v>18.890976999999999</v>
+      </c>
+      <c r="T50">
+        <v>3.1905960000000002</v>
+      </c>
+      <c r="U50">
+        <v>282</v>
+      </c>
+      <c r="V50">
+        <v>3.3825120000000002</v>
+      </c>
+      <c r="W50">
+        <v>17.819148999999999</v>
+      </c>
+    </row>
+    <row r="51" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>25</v>
+      </c>
+      <c r="B51" t="s">
+        <v>26</v>
+      </c>
+      <c r="C51" t="s">
+        <v>116</v>
+      </c>
+      <c r="D51" t="s">
+        <v>68</v>
+      </c>
+      <c r="E51" t="s">
+        <v>29</v>
+      </c>
+      <c r="F51">
+        <v>124</v>
+      </c>
+      <c r="G51" t="s">
+        <v>39</v>
+      </c>
+      <c r="H51">
+        <v>3482</v>
+      </c>
+      <c r="I51">
+        <v>1.6947159999999999</v>
+      </c>
+      <c r="J51">
+        <v>47.314516130000001</v>
+      </c>
+      <c r="K51" t="s">
+        <v>34</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51">
+        <v>5867</v>
+      </c>
+      <c r="N51" t="s">
+        <v>35</v>
+      </c>
+      <c r="O51">
+        <v>5901</v>
+      </c>
+      <c r="P51">
+        <v>994.23826499999996</v>
+      </c>
+      <c r="Q51">
+        <v>124</v>
+      </c>
+      <c r="S51">
+        <v>47.314515999999998</v>
+      </c>
+      <c r="T51">
+        <v>2.1013389999999998</v>
+      </c>
+      <c r="U51">
+        <v>162</v>
+      </c>
+      <c r="V51">
+        <v>2.7452969999999999</v>
+      </c>
+      <c r="W51">
+        <v>36.216048999999998</v>
+      </c>
+    </row>
+    <row r="52" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>25</v>
+      </c>
+      <c r="B52" t="s">
+        <v>26</v>
+      </c>
+      <c r="C52" t="s">
+        <v>117</v>
+      </c>
+      <c r="D52" t="s">
+        <v>68</v>
+      </c>
+      <c r="E52" t="s">
+        <v>29</v>
+      </c>
+      <c r="F52">
+        <v>172</v>
+      </c>
+      <c r="G52" t="s">
+        <v>39</v>
+      </c>
+      <c r="H52">
+        <v>2487</v>
+      </c>
+      <c r="I52">
+        <v>1.450342</v>
+      </c>
+      <c r="J52">
+        <v>28.156976740000001</v>
+      </c>
+      <c r="K52" t="s">
+        <v>34</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52">
+        <v>4843</v>
+      </c>
+      <c r="N52" t="s">
+        <v>114</v>
+      </c>
+      <c r="O52">
+        <v>3607</v>
+      </c>
+      <c r="P52">
+        <v>1342.6670360000001</v>
+      </c>
+      <c r="Q52">
+        <v>172</v>
+      </c>
+      <c r="S52">
+        <v>28.156977000000001</v>
+      </c>
+      <c r="T52">
+        <v>4.7685060000000004</v>
+      </c>
+      <c r="U52">
+        <v>187</v>
+      </c>
+      <c r="V52">
+        <v>5.1843640000000004</v>
+      </c>
+      <c r="W52">
+        <v>25.898396000000002</v>
+      </c>
+    </row>
+    <row r="53" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>25</v>
+      </c>
+      <c r="B53" t="s">
+        <v>26</v>
+      </c>
+      <c r="C53" t="s">
+        <v>118</v>
+      </c>
+      <c r="D53" t="s">
+        <v>68</v>
+      </c>
+      <c r="E53" t="s">
+        <v>29</v>
+      </c>
+      <c r="F53">
+        <v>447</v>
+      </c>
+      <c r="G53" t="s">
+        <v>39</v>
+      </c>
+      <c r="H53">
+        <v>5387</v>
+      </c>
+      <c r="I53">
+        <v>1.33321</v>
+      </c>
+      <c r="J53">
+        <v>12.422818790000001</v>
+      </c>
+      <c r="K53" t="s">
+        <v>34</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53">
+        <v>5553</v>
+      </c>
+      <c r="N53" t="s">
+        <v>35</v>
+      </c>
+      <c r="O53">
+        <v>7182</v>
+      </c>
+      <c r="P53">
+        <v>773.18295699999999</v>
+      </c>
+      <c r="Q53">
+        <v>447</v>
+      </c>
+      <c r="S53">
+        <v>12.422819</v>
+      </c>
+      <c r="T53">
+        <v>6.2238930000000003</v>
+      </c>
+      <c r="U53">
+        <v>488</v>
+      </c>
+      <c r="V53">
+        <v>6.7947649999999999</v>
+      </c>
+      <c r="W53">
+        <v>11.379098000000001</v>
+      </c>
+    </row>
+    <row r="54" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>25</v>
+      </c>
+      <c r="B54" t="s">
+        <v>26</v>
+      </c>
+      <c r="C54" t="s">
+        <v>119</v>
+      </c>
+      <c r="D54" t="s">
+        <v>68</v>
+      </c>
+      <c r="E54" t="s">
+        <v>29</v>
+      </c>
+      <c r="F54">
+        <v>130</v>
+      </c>
+      <c r="G54" t="s">
+        <v>39</v>
+      </c>
+      <c r="H54">
+        <v>4505</v>
+      </c>
+      <c r="I54">
+        <v>1.461265</v>
+      </c>
+      <c r="J54">
+        <v>41.876923079999997</v>
+      </c>
+      <c r="K54" t="s">
+        <v>34</v>
+      </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="M54">
+        <v>5444</v>
+      </c>
+      <c r="N54" t="s">
+        <v>35</v>
+      </c>
+      <c r="O54">
+        <v>6583</v>
+      </c>
+      <c r="P54">
+        <v>826.97858099999996</v>
+      </c>
+      <c r="Q54">
+        <v>130</v>
+      </c>
+      <c r="S54">
+        <v>41.876922999999998</v>
+      </c>
+      <c r="T54">
+        <v>1.9747840000000001</v>
+      </c>
+      <c r="U54">
+        <v>160</v>
+      </c>
+      <c r="V54">
+        <v>2.4305029999999999</v>
+      </c>
+      <c r="W54">
+        <v>34.024999999999999</v>
+      </c>
+    </row>
+    <row r="55" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>25</v>
+      </c>
+      <c r="B55" t="s">
+        <v>26</v>
+      </c>
+      <c r="C55" t="s">
+        <v>120</v>
+      </c>
+      <c r="D55" t="s">
+        <v>68</v>
+      </c>
+      <c r="E55" t="s">
+        <v>29</v>
+      </c>
+      <c r="F55">
+        <v>204</v>
+      </c>
+      <c r="G55" t="s">
+        <v>39</v>
+      </c>
+      <c r="H55">
+        <v>3081</v>
+      </c>
+      <c r="I55">
+        <v>1.8250569999999999</v>
+      </c>
+      <c r="J55">
+        <v>28.377450979999999</v>
+      </c>
+      <c r="K55" t="s">
+        <v>34</v>
+      </c>
+      <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55">
+        <v>5789</v>
+      </c>
+      <c r="N55" t="s">
+        <v>35</v>
+      </c>
+      <c r="O55">
+        <v>5623</v>
+      </c>
+      <c r="P55">
+        <v>1029.521608</v>
+      </c>
+      <c r="Q55">
+        <v>204</v>
+      </c>
+      <c r="S55">
+        <v>28.377451000000001</v>
+      </c>
+      <c r="T55">
+        <v>3.6279569999999999</v>
+      </c>
+      <c r="U55">
+        <v>248</v>
+      </c>
+      <c r="V55">
+        <v>4.4104570000000001</v>
+      </c>
+      <c r="W55">
+        <v>23.342742000000001</v>
+      </c>
+    </row>
+    <row r="56" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>25</v>
+      </c>
+      <c r="B56" t="s">
+        <v>26</v>
+      </c>
+      <c r="C56" t="s">
+        <v>121</v>
+      </c>
+      <c r="D56" t="s">
+        <v>68</v>
+      </c>
+      <c r="E56" t="s">
+        <v>29</v>
+      </c>
+      <c r="F56">
+        <v>260</v>
+      </c>
+      <c r="G56" t="s">
+        <v>39</v>
+      </c>
+      <c r="H56">
+        <v>4307</v>
+      </c>
+      <c r="I56">
+        <v>1.3689340000000001</v>
+      </c>
+      <c r="J56">
+        <v>20.96153846</v>
+      </c>
+      <c r="K56" t="s">
+        <v>34</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56">
+        <v>5450</v>
+      </c>
+      <c r="N56" t="s">
+        <v>67</v>
+      </c>
+      <c r="O56">
+        <v>5896</v>
+      </c>
+      <c r="P56">
+        <v>924.35549500000002</v>
+      </c>
+      <c r="Q56">
+        <v>260</v>
+      </c>
+      <c r="S56">
+        <v>20.961538000000001</v>
+      </c>
+      <c r="T56">
+        <v>4.4097689999999998</v>
+      </c>
+      <c r="U56">
+        <v>279</v>
+      </c>
+      <c r="V56">
+        <v>4.7320219999999997</v>
+      </c>
+      <c r="W56">
+        <v>19.534050000000001</v>
+      </c>
+    </row>
+    <row r="57" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>25</v>
+      </c>
+      <c r="B57" t="s">
+        <v>26</v>
+      </c>
+      <c r="C57" t="s">
+        <v>122</v>
+      </c>
+      <c r="D57" t="s">
+        <v>68</v>
+      </c>
+      <c r="E57" t="s">
+        <v>29</v>
+      </c>
+      <c r="F57">
+        <v>330</v>
+      </c>
+      <c r="G57" t="s">
+        <v>39</v>
+      </c>
+      <c r="H57">
+        <v>3370</v>
+      </c>
+      <c r="I57">
+        <v>1.4640949999999999</v>
+      </c>
+      <c r="J57">
+        <v>14.6030303</v>
+      </c>
+      <c r="K57">
+        <v>160</v>
+      </c>
+      <c r="L57" t="s">
+        <v>30</v>
+      </c>
+      <c r="M57">
+        <v>4819</v>
+      </c>
+      <c r="N57" t="s">
+        <v>62</v>
+      </c>
+      <c r="O57">
+        <v>4934</v>
+      </c>
+      <c r="P57">
+        <v>976.69233899999995</v>
+      </c>
+      <c r="Q57">
+        <v>330</v>
+      </c>
+      <c r="S57">
+        <v>14.60303</v>
+      </c>
+      <c r="T57">
+        <v>6.6882849999999996</v>
+      </c>
+      <c r="U57">
+        <v>362</v>
+      </c>
+      <c r="V57">
+        <v>7.3368460000000004</v>
+      </c>
+      <c r="W57">
+        <v>13.312155000000001</v>
+      </c>
+    </row>
+    <row r="58" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>25</v>
+      </c>
+      <c r="B58" t="s">
+        <v>26</v>
+      </c>
+      <c r="C58" t="s">
+        <v>123</v>
+      </c>
+      <c r="D58" t="s">
+        <v>68</v>
+      </c>
+      <c r="E58" t="s">
+        <v>29</v>
+      </c>
+      <c r="F58">
+        <v>106</v>
+      </c>
+      <c r="G58" t="s">
+        <v>39</v>
+      </c>
+      <c r="H58">
+        <v>3164</v>
+      </c>
+      <c r="I58">
+        <v>1.2537929999999999</v>
+      </c>
+      <c r="J58">
+        <v>45.698113210000002</v>
+      </c>
+      <c r="K58">
+        <v>160</v>
+      </c>
+      <c r="L58" t="s">
+        <v>30</v>
+      </c>
+      <c r="M58">
+        <v>4844</v>
+      </c>
+      <c r="N58" t="s">
+        <v>124</v>
+      </c>
+      <c r="O58">
+        <v>3967</v>
+      </c>
+      <c r="P58">
+        <v>1221.0738590000001</v>
+      </c>
+      <c r="Q58">
+        <v>106</v>
+      </c>
+      <c r="S58">
+        <v>45.698112999999999</v>
+      </c>
+      <c r="T58">
+        <v>2.6720440000000001</v>
+      </c>
+      <c r="U58">
+        <v>115</v>
+      </c>
+      <c r="V58">
+        <v>2.8989159999999998</v>
+      </c>
+      <c r="W58">
+        <v>42.121738999999998</v>
+      </c>
+      <c r="X58">
+        <v>77</v>
+      </c>
+      <c r="Y58">
+        <v>62.909090999999997</v>
+      </c>
+    </row>
+    <row r="59" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>25</v>
+      </c>
+      <c r="B59" t="s">
+        <v>26</v>
+      </c>
+      <c r="C59" t="s">
+        <v>125</v>
+      </c>
+      <c r="D59" t="s">
+        <v>68</v>
+      </c>
+      <c r="E59" t="s">
+        <v>29</v>
+      </c>
+      <c r="F59">
+        <v>241</v>
+      </c>
+      <c r="G59" t="s">
+        <v>39</v>
+      </c>
+      <c r="H59">
+        <v>3045</v>
+      </c>
+      <c r="I59">
+        <v>1.570443</v>
+      </c>
+      <c r="J59">
+        <v>19.97095436</v>
+      </c>
+      <c r="K59">
+        <v>160</v>
+      </c>
+      <c r="L59" t="s">
+        <v>30</v>
+      </c>
+      <c r="M59">
+        <v>4813</v>
+      </c>
+      <c r="N59" t="s">
+        <v>126</v>
+      </c>
+      <c r="O59">
+        <v>4782</v>
+      </c>
+      <c r="P59">
+        <v>1006.4826430000001</v>
+      </c>
+      <c r="Q59">
+        <v>241</v>
+      </c>
+      <c r="S59">
+        <v>19.970953999999999</v>
+      </c>
+      <c r="T59">
+        <v>5.0397319999999999</v>
+      </c>
+      <c r="U59">
+        <v>252</v>
+      </c>
+      <c r="V59">
+        <v>5.2697620000000001</v>
+      </c>
+      <c r="W59">
+        <v>19.099205999999999</v>
+      </c>
+      <c r="X59">
+        <v>201</v>
+      </c>
+      <c r="Y59">
+        <v>23.945274000000001</v>
+      </c>
+    </row>
+    <row r="60" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>25</v>
+      </c>
+      <c r="B60" t="s">
+        <v>26</v>
+      </c>
+      <c r="C60" t="s">
+        <v>127</v>
+      </c>
+      <c r="D60" t="s">
+        <v>68</v>
+      </c>
+      <c r="E60" t="s">
+        <v>29</v>
+      </c>
+      <c r="F60">
+        <v>198</v>
+      </c>
+      <c r="G60" t="s">
+        <v>39</v>
+      </c>
+      <c r="H60">
+        <v>4704</v>
+      </c>
+      <c r="I60">
+        <v>1.274022</v>
+      </c>
+      <c r="J60">
+        <v>24.429292929999999</v>
+      </c>
+      <c r="K60">
+        <v>160</v>
+      </c>
+      <c r="L60" t="s">
+        <v>30</v>
+      </c>
+      <c r="M60">
+        <v>4837</v>
+      </c>
+      <c r="N60" t="s">
+        <v>126</v>
+      </c>
+      <c r="O60">
+        <v>5993</v>
+      </c>
+      <c r="P60">
+        <v>807.108293</v>
+      </c>
+      <c r="Q60">
+        <v>198</v>
+      </c>
+      <c r="S60">
+        <v>24.429293000000001</v>
+      </c>
+      <c r="T60">
+        <v>3.303855</v>
+      </c>
+      <c r="U60">
+        <v>230</v>
+      </c>
+      <c r="V60">
+        <v>3.8378109999999999</v>
+      </c>
+      <c r="W60">
+        <v>21.030435000000001</v>
+      </c>
+      <c r="X60">
+        <v>161</v>
+      </c>
+      <c r="Y60">
+        <v>30.043478</v>
+      </c>
+    </row>
+    <row r="61" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>25</v>
+      </c>
+      <c r="B61" t="s">
+        <v>26</v>
+      </c>
+      <c r="C61" t="s">
+        <v>128</v>
+      </c>
+      <c r="D61" t="s">
+        <v>68</v>
+      </c>
+      <c r="E61" t="s">
+        <v>29</v>
+      </c>
+      <c r="F61">
+        <v>357</v>
+      </c>
+      <c r="G61" t="s">
+        <v>39</v>
+      </c>
+      <c r="H61">
+        <v>3887</v>
+      </c>
+      <c r="I61">
+        <v>1.806535</v>
+      </c>
+      <c r="J61">
+        <v>13.48459384</v>
+      </c>
+      <c r="K61">
+        <v>160</v>
+      </c>
+      <c r="L61" t="s">
+        <v>30</v>
+      </c>
+      <c r="M61">
+        <v>4814</v>
+      </c>
+      <c r="N61" t="s">
+        <v>126</v>
+      </c>
+      <c r="O61">
+        <v>7022</v>
+      </c>
+      <c r="P61">
+        <v>685.55966999999998</v>
+      </c>
+      <c r="Q61">
+        <v>357</v>
+      </c>
+      <c r="S61">
+        <v>13.484594</v>
+      </c>
+      <c r="T61">
+        <v>5.084022</v>
+      </c>
+      <c r="U61">
+        <v>463</v>
+      </c>
+      <c r="V61">
+        <v>6.5935629999999996</v>
+      </c>
+      <c r="W61">
+        <v>10.397408</v>
+      </c>
+      <c r="X61">
+        <v>13</v>
+      </c>
+      <c r="Y61">
+        <v>370.30769199999997</v>
+      </c>
+    </row>
+    <row r="62" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>25</v>
+      </c>
+      <c r="B62" t="s">
+        <v>26</v>
+      </c>
+      <c r="C62" t="s">
+        <v>129</v>
+      </c>
+      <c r="D62" t="s">
+        <v>68</v>
+      </c>
+      <c r="E62" t="s">
+        <v>29</v>
+      </c>
+      <c r="F62">
+        <v>194</v>
+      </c>
+      <c r="G62" t="s">
+        <v>39</v>
+      </c>
+      <c r="H62">
+        <v>3954</v>
+      </c>
+      <c r="I62">
+        <v>1.3722810000000001</v>
+      </c>
+      <c r="J62">
+        <v>24.695876290000001</v>
+      </c>
+      <c r="K62">
+        <v>160</v>
+      </c>
+      <c r="L62" t="s">
+        <v>30</v>
+      </c>
+      <c r="M62">
+        <v>4791</v>
+      </c>
+      <c r="N62" t="s">
+        <v>126</v>
+      </c>
+      <c r="O62">
+        <v>5426</v>
+      </c>
+      <c r="P62">
+        <v>882.97088099999996</v>
+      </c>
+      <c r="Q62">
+        <v>194</v>
+      </c>
+      <c r="S62">
+        <v>24.695875999999998</v>
+      </c>
+      <c r="T62">
+        <v>3.5753780000000002</v>
+      </c>
+      <c r="U62">
+        <v>233</v>
+      </c>
+      <c r="V62">
+        <v>4.2941390000000004</v>
+      </c>
+      <c r="W62">
+        <v>20.562232000000002</v>
+      </c>
+      <c r="X62">
+        <v>6</v>
+      </c>
+      <c r="Y62">
+        <v>798.5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>25</v>
+      </c>
+      <c r="B63" t="s">
+        <v>26</v>
+      </c>
+      <c r="C63" t="s">
+        <v>130</v>
+      </c>
+      <c r="D63" t="s">
+        <v>68</v>
+      </c>
+      <c r="E63" t="s">
+        <v>29</v>
+      </c>
+      <c r="F63">
+        <v>343</v>
+      </c>
+      <c r="G63" t="s">
+        <v>39</v>
+      </c>
+      <c r="H63">
+        <v>5789</v>
+      </c>
+      <c r="I63">
+        <v>1.346347</v>
+      </c>
+      <c r="J63">
+        <v>14.00291545</v>
+      </c>
+      <c r="K63">
+        <v>160</v>
+      </c>
+      <c r="L63" t="s">
+        <v>30</v>
+      </c>
+      <c r="M63">
+        <v>4803</v>
+      </c>
+      <c r="N63" t="s">
+        <v>126</v>
+      </c>
+      <c r="O63">
+        <v>7794</v>
+      </c>
+      <c r="P63">
+        <v>616.24326399999995</v>
+      </c>
+      <c r="Q63">
+        <v>343</v>
+      </c>
+      <c r="S63">
+        <v>14.002915</v>
+      </c>
+      <c r="T63">
+        <v>4.4008209999999996</v>
+      </c>
+      <c r="U63">
+        <v>393</v>
+      </c>
+      <c r="V63">
+        <v>5.0423400000000003</v>
+      </c>
+      <c r="W63">
+        <v>12.221374000000001</v>
+      </c>
+      <c r="X63">
+        <v>284</v>
+      </c>
+      <c r="Y63">
+        <v>16.911971999999999</v>
+      </c>
+    </row>
+    <row r="64" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>25</v>
+      </c>
+      <c r="B64" t="s">
+        <v>26</v>
+      </c>
+      <c r="C64" t="s">
+        <v>131</v>
+      </c>
+      <c r="D64" t="s">
+        <v>68</v>
+      </c>
+      <c r="E64" t="s">
+        <v>29</v>
+      </c>
+      <c r="F64">
+        <v>307</v>
+      </c>
+      <c r="G64" t="s">
+        <v>39</v>
+      </c>
+      <c r="H64">
+        <v>5732</v>
+      </c>
+      <c r="I64">
+        <v>1.2229589999999999</v>
+      </c>
+      <c r="J64">
+        <v>15.684039090000001</v>
+      </c>
+      <c r="K64">
+        <v>160</v>
+      </c>
+      <c r="L64" t="s">
+        <v>30</v>
+      </c>
+      <c r="M64">
+        <v>4815</v>
+      </c>
+      <c r="N64" t="s">
+        <v>126</v>
+      </c>
+      <c r="O64">
+        <v>7010</v>
+      </c>
+      <c r="P64">
+        <v>686.87589200000002</v>
+      </c>
+      <c r="Q64">
+        <v>307</v>
+      </c>
+      <c r="S64">
+        <v>15.684039</v>
+      </c>
+      <c r="T64">
+        <v>4.3794579999999996</v>
+      </c>
+      <c r="U64">
+        <v>372</v>
+      </c>
+      <c r="V64">
+        <v>5.306705</v>
+      </c>
+      <c r="W64">
+        <v>12.943548</v>
+      </c>
+      <c r="X64">
+        <v>245</v>
+      </c>
+      <c r="Y64">
+        <v>19.653061000000001</v>
+      </c>
+    </row>
+    <row r="65" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>25</v>
+      </c>
+      <c r="B65" t="s">
+        <v>26</v>
+      </c>
+      <c r="C65" t="s">
+        <v>132</v>
+      </c>
+      <c r="D65" t="s">
+        <v>68</v>
+      </c>
+      <c r="E65" t="s">
+        <v>29</v>
+      </c>
+      <c r="F65">
+        <v>61</v>
+      </c>
+      <c r="G65" t="s">
+        <v>39</v>
+      </c>
+      <c r="H65">
+        <v>2335</v>
+      </c>
+      <c r="I65">
+        <v>1.6591009999999999</v>
+      </c>
+      <c r="J65">
+        <v>79.098360659999997</v>
+      </c>
+      <c r="K65">
+        <v>160</v>
+      </c>
+      <c r="L65" t="s">
+        <v>30</v>
+      </c>
+      <c r="M65">
+        <v>4825</v>
+      </c>
+      <c r="N65" t="s">
+        <v>126</v>
+      </c>
+      <c r="O65">
+        <v>3874</v>
+      </c>
+      <c r="P65">
+        <v>1245.4827049999999</v>
+      </c>
+      <c r="Q65">
+        <v>61</v>
+      </c>
+      <c r="S65">
+        <v>79.098360999999997</v>
+      </c>
+      <c r="T65">
+        <v>1.5746</v>
+      </c>
+      <c r="U65">
+        <v>62</v>
+      </c>
+      <c r="V65">
+        <v>1.6004130000000001</v>
+      </c>
+      <c r="W65">
+        <v>77.822581</v>
+      </c>
+      <c r="X65">
+        <v>50</v>
+      </c>
+      <c r="Y65">
+        <v>96.5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>25</v>
+      </c>
+      <c r="B66" t="s">
+        <v>26</v>
+      </c>
+      <c r="C66" t="s">
+        <v>133</v>
+      </c>
+      <c r="D66" t="s">
+        <v>68</v>
+      </c>
+      <c r="E66" t="s">
+        <v>29</v>
+      </c>
+      <c r="F66">
+        <v>697</v>
+      </c>
+      <c r="G66" t="s">
+        <v>39</v>
+      </c>
+      <c r="H66">
+        <v>10068</v>
+      </c>
+      <c r="I66">
+        <v>1.114819</v>
+      </c>
+      <c r="J66">
+        <v>6.90817791</v>
+      </c>
+      <c r="K66">
+        <v>160</v>
+      </c>
+      <c r="L66" t="s">
+        <v>30</v>
+      </c>
+      <c r="M66">
+        <v>4815</v>
+      </c>
+      <c r="N66" t="s">
+        <v>126</v>
+      </c>
+      <c r="O66">
+        <v>11224</v>
+      </c>
+      <c r="P66">
+        <v>428.99144699999999</v>
+      </c>
+      <c r="Q66">
+        <v>697</v>
+      </c>
+      <c r="S66">
+        <v>6.9081780000000004</v>
+      </c>
+      <c r="T66">
+        <v>6.2099070000000003</v>
+      </c>
+      <c r="U66">
+        <v>775</v>
+      </c>
+      <c r="V66">
+        <v>6.9048470000000002</v>
+      </c>
+      <c r="W66">
+        <v>6.2129029999999998</v>
+      </c>
+      <c r="X66">
+        <v>505</v>
+      </c>
+      <c r="Y66">
+        <v>9.5346530000000005</v>
+      </c>
+    </row>
+    <row r="67" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>25</v>
+      </c>
+      <c r="B67" t="s">
+        <v>26</v>
+      </c>
+      <c r="C67" t="s">
+        <v>134</v>
+      </c>
+      <c r="D67" t="s">
+        <v>28</v>
+      </c>
+      <c r="E67" t="s">
+        <v>29</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <v>160</v>
+      </c>
+      <c r="L67" t="s">
+        <v>30</v>
+      </c>
+      <c r="M67">
+        <v>0</v>
+      </c>
+      <c r="N67" t="s">
+        <v>126</v>
+      </c>
+      <c r="O67">
+        <v>0</v>
+      </c>
+      <c r="P67">
+        <v>0</v>
+      </c>
+      <c r="U67">
+        <v>0</v>
+      </c>
+      <c r="V67">
+        <v>0</v>
+      </c>
+      <c r="W67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>25</v>
+      </c>
+      <c r="B68" t="s">
+        <v>26</v>
+      </c>
+      <c r="C68" t="s">
+        <v>135</v>
+      </c>
+      <c r="D68" t="s">
+        <v>68</v>
+      </c>
+      <c r="E68" t="s">
+        <v>29</v>
+      </c>
+      <c r="F68">
+        <v>280</v>
+      </c>
+      <c r="G68" t="s">
+        <v>39</v>
+      </c>
+      <c r="H68">
+        <v>4283</v>
+      </c>
+      <c r="I68">
+        <v>1.351389</v>
+      </c>
+      <c r="J68">
+        <v>17.178571430000002</v>
+      </c>
+      <c r="K68">
+        <v>160</v>
+      </c>
+      <c r="L68" t="s">
+        <v>30</v>
+      </c>
+      <c r="M68">
+        <v>4810</v>
+      </c>
+      <c r="N68" t="s">
+        <v>126</v>
+      </c>
+      <c r="O68">
+        <v>5788</v>
+      </c>
+      <c r="P68">
+        <v>831.02971700000001</v>
+      </c>
+      <c r="Q68">
+        <v>280</v>
+      </c>
+      <c r="S68">
+        <v>17.178571000000002</v>
+      </c>
+      <c r="T68">
+        <v>4.8375950000000003</v>
+      </c>
+      <c r="U68">
+        <v>293</v>
+      </c>
+      <c r="V68">
+        <v>5.0621980000000004</v>
+      </c>
+      <c r="W68">
+        <v>16.416381999999999</v>
+      </c>
+      <c r="X68">
+        <v>69</v>
+      </c>
+      <c r="Y68">
+        <v>69.710144999999997</v>
+      </c>
+    </row>
+    <row r="69" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>25</v>
+      </c>
+      <c r="B69" t="s">
+        <v>26</v>
+      </c>
+      <c r="C69" t="s">
+        <v>136</v>
+      </c>
+      <c r="D69" t="s">
+        <v>68</v>
+      </c>
+      <c r="E69" t="s">
+        <v>29</v>
+      </c>
+      <c r="F69">
+        <v>183</v>
+      </c>
+      <c r="G69" t="s">
+        <v>39</v>
+      </c>
+      <c r="H69">
+        <v>5471</v>
+      </c>
+      <c r="I69">
+        <v>1.3149329999999999</v>
+      </c>
+      <c r="J69">
+        <v>26.31693989</v>
+      </c>
+      <c r="K69">
+        <v>160</v>
+      </c>
+      <c r="L69" t="s">
+        <v>30</v>
+      </c>
+      <c r="M69">
+        <v>4816</v>
+      </c>
+      <c r="N69" t="s">
+        <v>126</v>
+      </c>
+      <c r="O69">
+        <v>7194</v>
+      </c>
+      <c r="P69">
+        <v>669.44676100000004</v>
+      </c>
+      <c r="Q69">
+        <v>183</v>
+      </c>
+      <c r="S69">
+        <v>26.316939999999999</v>
+      </c>
+      <c r="T69">
+        <v>2.5437859999999999</v>
+      </c>
+      <c r="U69">
+        <v>231</v>
+      </c>
+      <c r="V69">
+        <v>3.2110089999999998</v>
+      </c>
+      <c r="W69">
+        <v>20.848485</v>
+      </c>
+      <c r="X69">
+        <v>144</v>
+      </c>
+      <c r="Y69">
+        <v>33.444443999999997</v>
+      </c>
+    </row>
+    <row r="70" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>25</v>
+      </c>
+      <c r="B70" t="s">
+        <v>26</v>
+      </c>
+      <c r="C70" t="s">
+        <v>137</v>
+      </c>
+      <c r="D70" t="s">
+        <v>68</v>
+      </c>
+      <c r="E70" t="s">
+        <v>29</v>
+      </c>
+      <c r="F70">
+        <v>63</v>
+      </c>
+      <c r="G70" t="s">
+        <v>39</v>
+      </c>
+      <c r="H70">
+        <v>4523</v>
+      </c>
+      <c r="I70">
+        <v>1.390007</v>
+      </c>
+      <c r="J70">
+        <v>76.047619049999994</v>
+      </c>
+      <c r="K70">
+        <v>160</v>
+      </c>
+      <c r="L70" t="s">
+        <v>30</v>
+      </c>
+      <c r="M70">
+        <v>4791</v>
+      </c>
+      <c r="N70" t="s">
+        <v>126</v>
+      </c>
+      <c r="O70">
+        <v>6287</v>
+      </c>
+      <c r="P70">
+        <v>762.04867200000001</v>
+      </c>
+      <c r="Q70">
+        <v>63</v>
+      </c>
+      <c r="S70">
+        <v>76.047618999999997</v>
+      </c>
+      <c r="T70">
+        <v>1.002068</v>
+      </c>
+      <c r="U70">
+        <v>77</v>
+      </c>
+      <c r="V70">
+        <v>1.2247490000000001</v>
+      </c>
+      <c r="W70">
+        <v>62.220779</v>
+      </c>
+      <c r="X70">
+        <v>4</v>
+      </c>
+      <c r="Y70">
+        <v>1197.75</v>
+      </c>
+    </row>
+    <row r="71" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>25</v>
+      </c>
+      <c r="B71" t="s">
+        <v>26</v>
+      </c>
+      <c r="C71" t="s">
+        <v>138</v>
+      </c>
+      <c r="D71" t="s">
+        <v>68</v>
+      </c>
+      <c r="E71" t="s">
+        <v>29</v>
+      </c>
+      <c r="F71">
+        <v>341</v>
+      </c>
+      <c r="G71" t="s">
+        <v>39</v>
+      </c>
+      <c r="H71">
+        <v>5467</v>
+      </c>
+      <c r="I71">
+        <v>1.2037679999999999</v>
+      </c>
+      <c r="J71">
+        <v>14.12609971</v>
+      </c>
+      <c r="K71">
+        <v>160</v>
+      </c>
+      <c r="L71" t="s">
+        <v>30</v>
+      </c>
+      <c r="M71">
+        <v>4817</v>
+      </c>
+      <c r="N71" t="s">
+        <v>126</v>
+      </c>
+      <c r="O71">
+        <v>6581</v>
+      </c>
+      <c r="P71">
+        <v>731.95563000000004</v>
+      </c>
+      <c r="Q71">
+        <v>341</v>
+      </c>
+      <c r="S71">
+        <v>14.126099999999999</v>
+      </c>
+      <c r="T71">
+        <v>5.1815829999999998</v>
+      </c>
+      <c r="U71">
+        <v>372</v>
+      </c>
+      <c r="V71">
+        <v>5.6526360000000002</v>
+      </c>
+      <c r="W71">
+        <v>12.948924999999999</v>
+      </c>
+      <c r="X71">
+        <v>291</v>
+      </c>
+      <c r="Y71">
+        <v>16.553265</v>
+      </c>
+    </row>
+    <row r="72" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>25</v>
+      </c>
+      <c r="B72" t="s">
+        <v>26</v>
+      </c>
+      <c r="C72" t="s">
+        <v>139</v>
+      </c>
+      <c r="D72" t="s">
+        <v>28</v>
+      </c>
+      <c r="E72" t="s">
+        <v>29</v>
+      </c>
+      <c r="H72">
+        <v>0</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="K72">
+        <v>160</v>
+      </c>
+      <c r="L72" t="s">
+        <v>30</v>
+      </c>
+      <c r="M72">
+        <v>0</v>
+      </c>
+      <c r="N72" t="s">
+        <v>126</v>
+      </c>
+      <c r="O72">
+        <v>0</v>
+      </c>
+      <c r="P72">
+        <v>0</v>
+      </c>
+      <c r="U72">
+        <v>0</v>
+      </c>
+      <c r="V72">
+        <v>0</v>
+      </c>
+      <c r="W72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>25</v>
+      </c>
+      <c r="B73" t="s">
+        <v>26</v>
+      </c>
+      <c r="C73" t="s">
+        <v>140</v>
+      </c>
+      <c r="D73" t="s">
+        <v>28</v>
+      </c>
+      <c r="E73" t="s">
+        <v>29</v>
+      </c>
+      <c r="F73">
+        <v>15</v>
+      </c>
+      <c r="G73" t="s">
+        <v>39</v>
+      </c>
+      <c r="H73">
+        <v>516</v>
+      </c>
+      <c r="I73">
+        <v>1.0910850000000001</v>
+      </c>
+      <c r="J73">
+        <v>45.2</v>
+      </c>
+      <c r="K73">
+        <v>160</v>
+      </c>
+      <c r="L73" t="s">
+        <v>30</v>
+      </c>
+      <c r="M73">
+        <v>678</v>
+      </c>
+      <c r="N73" t="s">
+        <v>141</v>
+      </c>
+      <c r="O73">
+        <v>563</v>
+      </c>
+      <c r="P73">
+        <v>1204.2628769999999</v>
+      </c>
+      <c r="Q73">
+        <v>15</v>
+      </c>
+      <c r="S73">
+        <v>45.2</v>
+      </c>
+      <c r="T73">
+        <v>2.6642980000000001</v>
+      </c>
+      <c r="U73">
+        <v>15</v>
+      </c>
+      <c r="V73">
+        <v>2.6642980000000001</v>
+      </c>
+      <c r="W73">
+        <v>45.2</v>
+      </c>
+      <c r="X73">
+        <v>9</v>
+      </c>
+      <c r="Y73">
+        <v>75.333332999999996</v>
+      </c>
+    </row>
+    <row r="74" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>25</v>
+      </c>
+      <c r="B74" t="s">
+        <v>26</v>
+      </c>
+      <c r="C74" t="s">
+        <v>142</v>
+      </c>
+      <c r="D74" t="s">
+        <v>143</v>
+      </c>
+      <c r="E74" t="s">
+        <v>29</v>
+      </c>
+      <c r="F74">
+        <v>179</v>
+      </c>
+      <c r="G74" t="s">
+        <v>39</v>
+      </c>
+      <c r="H74">
+        <v>2234</v>
+      </c>
+      <c r="I74">
+        <v>1.3692930000000001</v>
+      </c>
+      <c r="J74">
+        <v>26.960893850000001</v>
+      </c>
+      <c r="K74">
+        <v>160</v>
+      </c>
+      <c r="L74" t="s">
+        <v>30</v>
+      </c>
+      <c r="M74">
+        <v>4826</v>
+      </c>
+      <c r="N74" t="s">
+        <v>82</v>
+      </c>
+      <c r="O74">
+        <v>3059</v>
+      </c>
+      <c r="P74">
+        <v>1577.639752</v>
+      </c>
+      <c r="Q74">
+        <v>179</v>
+      </c>
+      <c r="S74">
+        <v>26.960894</v>
+      </c>
+      <c r="T74">
+        <v>5.851585</v>
+      </c>
+      <c r="U74">
+        <v>183</v>
+      </c>
+      <c r="V74">
+        <v>5.9823469999999999</v>
+      </c>
+      <c r="W74">
+        <v>26.371585</v>
+      </c>
+      <c r="X74">
+        <v>152</v>
+      </c>
+      <c r="Y74">
+        <v>31.75</v>
+      </c>
+    </row>
+    <row r="75" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>25</v>
+      </c>
+      <c r="B75" t="s">
+        <v>26</v>
+      </c>
+      <c r="C75" t="s">
+        <v>144</v>
+      </c>
+      <c r="D75" t="s">
+        <v>38</v>
+      </c>
+      <c r="E75" t="s">
+        <v>29</v>
+      </c>
+      <c r="F75">
+        <v>111</v>
+      </c>
+      <c r="G75" t="s">
+        <v>39</v>
+      </c>
+      <c r="H75">
+        <v>3982</v>
+      </c>
+      <c r="I75">
+        <v>1.3518330000000001</v>
+      </c>
+      <c r="J75">
+        <v>43.315315320000003</v>
+      </c>
+      <c r="K75">
+        <v>160</v>
+      </c>
+      <c r="L75" t="s">
+        <v>30</v>
+      </c>
+      <c r="M75">
+        <v>4808</v>
+      </c>
+      <c r="N75" t="s">
+        <v>85</v>
+      </c>
+      <c r="O75">
+        <v>5383</v>
+      </c>
+      <c r="P75">
+        <v>893.18223999999998</v>
+      </c>
+      <c r="Q75">
+        <v>111</v>
+      </c>
+      <c r="S75">
+        <v>43.315314999999998</v>
+      </c>
+      <c r="T75">
+        <v>2.0620470000000002</v>
+      </c>
+      <c r="U75">
+        <v>148</v>
+      </c>
+      <c r="V75">
+        <v>2.749396</v>
+      </c>
+      <c r="W75">
+        <v>32.486485999999999</v>
+      </c>
+      <c r="X75">
+        <v>12</v>
+      </c>
+      <c r="Y75">
+        <v>400.66666700000002</v>
+      </c>
+    </row>
+    <row r="76" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>25</v>
+      </c>
+      <c r="B76" t="s">
+        <v>26</v>
+      </c>
+      <c r="C76" t="s">
+        <v>144</v>
+      </c>
+      <c r="D76" t="s">
+        <v>38</v>
+      </c>
+      <c r="E76" t="s">
+        <v>29</v>
+      </c>
+      <c r="F76">
+        <v>147</v>
+      </c>
+      <c r="G76" t="s">
+        <v>39</v>
+      </c>
+      <c r="H76">
+        <v>3654</v>
+      </c>
+      <c r="I76">
+        <v>1.4378759999999999</v>
+      </c>
+      <c r="J76">
+        <v>32.83673469</v>
+      </c>
+      <c r="K76">
+        <v>160</v>
+      </c>
+      <c r="L76" t="s">
+        <v>30</v>
+      </c>
+      <c r="M76">
+        <v>4827</v>
+      </c>
+      <c r="N76" t="s">
+        <v>85</v>
+      </c>
+      <c r="O76">
+        <v>5254</v>
+      </c>
+      <c r="P76">
+        <v>918.72858799999995</v>
+      </c>
+      <c r="Q76">
+        <v>147</v>
+      </c>
+      <c r="S76">
+        <v>32.836734999999997</v>
+      </c>
+      <c r="T76">
+        <v>2.7978679999999998</v>
+      </c>
+      <c r="U76">
+        <v>194</v>
+      </c>
+      <c r="V76">
+        <v>3.6924250000000001</v>
+      </c>
+      <c r="W76">
+        <v>24.881443000000001</v>
+      </c>
+      <c r="X76">
+        <v>123</v>
+      </c>
+      <c r="Y76">
+        <v>39.243901999999999</v>
+      </c>
+    </row>
+    <row r="77" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>25</v>
+      </c>
+      <c r="B77" t="s">
+        <v>26</v>
+      </c>
+      <c r="C77" t="s">
+        <v>145</v>
+      </c>
+      <c r="D77" t="s">
+        <v>38</v>
+      </c>
+      <c r="E77" t="s">
+        <v>29</v>
+      </c>
+      <c r="F77">
+        <v>221</v>
+      </c>
+      <c r="G77" t="s">
+        <v>39</v>
+      </c>
+      <c r="H77">
+        <v>2963</v>
+      </c>
+      <c r="I77">
+        <v>1.585218</v>
+      </c>
+      <c r="J77">
+        <v>21.84615385</v>
+      </c>
+      <c r="K77">
+        <v>160</v>
+      </c>
+      <c r="L77" t="s">
+        <v>30</v>
+      </c>
+      <c r="M77">
+        <v>4828</v>
+      </c>
+      <c r="N77" t="s">
+        <v>85</v>
+      </c>
+      <c r="O77">
+        <v>4697</v>
+      </c>
+      <c r="P77">
+        <v>1027.8901430000001</v>
+      </c>
+      <c r="Q77">
+        <v>221</v>
+      </c>
+      <c r="S77">
+        <v>21.846153999999999</v>
+      </c>
+      <c r="T77">
+        <v>4.7051309999999997</v>
+      </c>
+      <c r="U77">
+        <v>237</v>
+      </c>
+      <c r="V77">
+        <v>5.0457739999999998</v>
+      </c>
+      <c r="W77">
+        <v>20.371307999999999</v>
+      </c>
+      <c r="X77">
+        <v>185</v>
+      </c>
+      <c r="Y77">
+        <v>26.097297000000001</v>
+      </c>
+    </row>
+    <row r="78" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>25</v>
+      </c>
+      <c r="B78" t="s">
+        <v>26</v>
+      </c>
+      <c r="C78" t="s">
+        <v>146</v>
+      </c>
+      <c r="D78" t="s">
+        <v>38</v>
+      </c>
+      <c r="E78" t="s">
+        <v>29</v>
+      </c>
+      <c r="F78">
+        <v>217</v>
+      </c>
+      <c r="G78" t="s">
+        <v>39</v>
+      </c>
+      <c r="H78">
+        <v>3521</v>
+      </c>
+      <c r="I78">
+        <v>1.4257310000000001</v>
+      </c>
+      <c r="J78">
+        <v>22.19354839</v>
+      </c>
+      <c r="K78">
+        <v>160</v>
+      </c>
+      <c r="L78" t="s">
+        <v>30</v>
+      </c>
+      <c r="M78">
+        <v>4816</v>
+      </c>
+      <c r="N78" t="s">
+        <v>85</v>
+      </c>
+      <c r="O78">
+        <v>5020</v>
+      </c>
+      <c r="P78">
+        <v>959.36255000000006</v>
+      </c>
+      <c r="Q78">
+        <v>217</v>
+      </c>
+      <c r="S78">
+        <v>22.193548</v>
+      </c>
+      <c r="T78">
+        <v>4.3227089999999997</v>
+      </c>
+      <c r="U78">
+        <v>286</v>
+      </c>
+      <c r="V78">
+        <v>5.6972110000000002</v>
+      </c>
+      <c r="W78">
+        <v>16.839161000000001</v>
+      </c>
+      <c r="X78">
+        <v>189</v>
+      </c>
+      <c r="Y78">
+        <v>25.481480999999999</v>
+      </c>
+    </row>
+    <row r="79" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>25</v>
+      </c>
+      <c r="B79" t="s">
+        <v>26</v>
+      </c>
+      <c r="C79" t="s">
+        <v>147</v>
+      </c>
+      <c r="D79" t="s">
+        <v>38</v>
+      </c>
+      <c r="E79" t="s">
+        <v>29</v>
+      </c>
+      <c r="F79">
+        <v>163</v>
+      </c>
+      <c r="G79" t="s">
+        <v>39</v>
+      </c>
+      <c r="H79">
+        <v>3996</v>
+      </c>
+      <c r="I79">
+        <v>1.5217719999999999</v>
+      </c>
+      <c r="J79">
+        <v>29.650306749999999</v>
+      </c>
+      <c r="K79">
+        <v>160</v>
+      </c>
+      <c r="L79" t="s">
+        <v>30</v>
+      </c>
+      <c r="M79">
+        <v>4833</v>
+      </c>
+      <c r="N79" t="s">
+        <v>85</v>
+      </c>
+      <c r="O79">
+        <v>6081</v>
+      </c>
+      <c r="P79">
+        <v>794.77059699999995</v>
+      </c>
+      <c r="Q79">
+        <v>163</v>
+      </c>
+      <c r="S79">
+        <v>29.650307000000002</v>
+      </c>
+      <c r="T79">
+        <v>2.6804800000000002</v>
+      </c>
+      <c r="U79">
+        <v>205</v>
+      </c>
+      <c r="V79">
+        <v>3.371156</v>
+      </c>
+      <c r="W79">
+        <v>23.575610000000001</v>
+      </c>
+      <c r="X79">
+        <v>143</v>
+      </c>
+      <c r="Y79">
+        <v>33.797203000000003</v>
+      </c>
+    </row>
+    <row r="80" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>25</v>
+      </c>
+      <c r="B80" t="s">
+        <v>26</v>
+      </c>
+      <c r="C80" t="s">
+        <v>148</v>
+      </c>
+      <c r="D80" t="s">
+        <v>28</v>
+      </c>
+      <c r="E80" t="s">
+        <v>29</v>
+      </c>
+      <c r="F80">
+        <v>28</v>
+      </c>
+      <c r="G80" t="s">
+        <v>39</v>
+      </c>
+      <c r="H80">
+        <v>955</v>
+      </c>
+      <c r="I80">
+        <v>1.1947639999999999</v>
+      </c>
+      <c r="J80">
+        <v>38</v>
+      </c>
+      <c r="K80">
+        <v>160</v>
+      </c>
+      <c r="L80" t="s">
+        <v>30</v>
+      </c>
+      <c r="M80">
+        <v>1064</v>
+      </c>
+      <c r="N80" t="s">
+        <v>85</v>
+      </c>
+      <c r="O80">
+        <v>1141</v>
+      </c>
+      <c r="P80">
+        <v>932.51533700000005</v>
+      </c>
+      <c r="Q80">
+        <v>28</v>
+      </c>
+      <c r="S80">
+        <v>38</v>
+      </c>
+      <c r="T80">
+        <v>2.4539879999999998</v>
+      </c>
+      <c r="U80">
+        <v>29</v>
+      </c>
+      <c r="V80">
+        <v>2.5416300000000001</v>
+      </c>
+      <c r="W80">
+        <v>36.689655000000002</v>
+      </c>
+      <c r="X80">
+        <v>24</v>
+      </c>
+      <c r="Y80">
+        <v>44.333333000000003</v>
+      </c>
+    </row>
+    <row r="81" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>25</v>
+      </c>
+      <c r="B81" t="s">
+        <v>26</v>
+      </c>
+      <c r="C81" t="s">
+        <v>149</v>
+      </c>
+      <c r="D81" t="s">
+        <v>28</v>
+      </c>
+      <c r="E81" t="s">
+        <v>29</v>
+      </c>
+      <c r="F81">
+        <v>25</v>
+      </c>
+      <c r="G81" t="s">
+        <v>39</v>
+      </c>
+      <c r="H81">
+        <v>1044</v>
+      </c>
+      <c r="I81">
+        <v>1.1561300000000001</v>
+      </c>
+      <c r="J81">
+        <v>42.88</v>
+      </c>
+      <c r="K81">
+        <v>160</v>
+      </c>
+      <c r="L81" t="s">
+        <v>30</v>
+      </c>
+      <c r="M81">
+        <v>1072</v>
+      </c>
+      <c r="N81" t="s">
+        <v>85</v>
+      </c>
+      <c r="O81">
+        <v>1207</v>
+      </c>
+      <c r="P81">
+        <v>888.15244399999995</v>
+      </c>
+      <c r="Q81">
+        <v>25</v>
+      </c>
+      <c r="S81">
+        <v>42.88</v>
+      </c>
+      <c r="T81">
+        <v>2.0712510000000002</v>
+      </c>
+      <c r="U81">
+        <v>27</v>
+      </c>
+      <c r="V81">
+        <v>2.2369509999999999</v>
+      </c>
+      <c r="W81">
+        <v>39.703704000000002</v>
+      </c>
+      <c r="X81">
+        <v>19</v>
+      </c>
+      <c r="Y81">
+        <v>56.421053000000001</v>
+      </c>
+    </row>
+    <row r="82" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>25</v>
+      </c>
+      <c r="B82" t="s">
+        <v>26</v>
+      </c>
+      <c r="C82" t="s">
+        <v>150</v>
+      </c>
+      <c r="D82" t="s">
+        <v>38</v>
+      </c>
+      <c r="E82" t="s">
+        <v>29</v>
+      </c>
+      <c r="F82">
+        <v>435</v>
+      </c>
+      <c r="G82" t="s">
+        <v>39</v>
+      </c>
+      <c r="H82">
+        <v>3173</v>
+      </c>
+      <c r="I82">
+        <v>1.5174909999999999</v>
+      </c>
+      <c r="J82">
+        <v>11.022988509999999</v>
+      </c>
+      <c r="K82">
+        <v>160</v>
+      </c>
+      <c r="L82" t="s">
+        <v>30</v>
+      </c>
+      <c r="M82">
+        <v>4795</v>
+      </c>
+      <c r="N82" t="s">
+        <v>151</v>
+      </c>
+      <c r="O82">
+        <v>4815</v>
+      </c>
+      <c r="P82">
+        <v>995.84631400000001</v>
+      </c>
+      <c r="Q82">
+        <v>435</v>
+      </c>
+      <c r="S82">
+        <v>11.022989000000001</v>
+      </c>
+      <c r="T82">
+        <v>9.0342680000000009</v>
+      </c>
+      <c r="U82">
+        <v>511</v>
+      </c>
+      <c r="V82">
+        <v>10.612669</v>
+      </c>
+      <c r="W82">
+        <v>9.3835619999999995</v>
+      </c>
+      <c r="X82">
+        <v>8</v>
+      </c>
+      <c r="Y82">
+        <v>599.375</v>
+      </c>
+    </row>
+    <row r="83" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>25</v>
+      </c>
+      <c r="B83" t="s">
+        <v>26</v>
+      </c>
+      <c r="C83" t="s">
+        <v>152</v>
+      </c>
+      <c r="D83" t="s">
+        <v>38</v>
+      </c>
+      <c r="E83" t="s">
+        <v>29</v>
+      </c>
+      <c r="F83">
+        <v>62</v>
+      </c>
+      <c r="G83" t="s">
+        <v>39</v>
+      </c>
+      <c r="H83">
+        <v>2450</v>
+      </c>
+      <c r="I83">
+        <v>1.9534689999999999</v>
+      </c>
+      <c r="J83">
+        <v>78.064516130000001</v>
+      </c>
+      <c r="K83">
+        <v>160</v>
+      </c>
+      <c r="L83" t="s">
+        <v>30</v>
+      </c>
+      <c r="M83">
+        <v>4840</v>
+      </c>
+      <c r="N83" t="s">
+        <v>85</v>
+      </c>
+      <c r="O83">
+        <v>4786</v>
+      </c>
+      <c r="P83">
+        <v>1011.282908</v>
+      </c>
+      <c r="Q83">
+        <v>62</v>
+      </c>
+      <c r="S83">
+        <v>78.064515999999998</v>
+      </c>
+      <c r="T83">
+        <v>1.295445</v>
+      </c>
+      <c r="U83">
+        <v>73</v>
+      </c>
+      <c r="V83">
+        <v>1.525282</v>
+      </c>
+      <c r="W83">
+        <v>66.301370000000006</v>
+      </c>
+      <c r="X83">
+        <v>40</v>
+      </c>
+      <c r="Y83">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="84" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>25</v>
+      </c>
+      <c r="B84" t="s">
+        <v>26</v>
+      </c>
+      <c r="C84" t="s">
+        <v>153</v>
+      </c>
+      <c r="D84" t="s">
+        <v>38</v>
+      </c>
+      <c r="E84" t="s">
+        <v>29</v>
+      </c>
+      <c r="F84">
+        <v>201</v>
+      </c>
+      <c r="G84" t="s">
+        <v>39</v>
+      </c>
+      <c r="H84">
+        <v>2587</v>
+      </c>
+      <c r="I84">
+        <v>1.549285</v>
+      </c>
+      <c r="J84">
+        <v>23.990049750000001</v>
+      </c>
+      <c r="K84">
+        <v>160</v>
+      </c>
+      <c r="L84" t="s">
+        <v>30</v>
+      </c>
+      <c r="M84">
+        <v>4822</v>
+      </c>
+      <c r="N84" t="s">
+        <v>85</v>
+      </c>
+      <c r="O84">
+        <v>4008</v>
+      </c>
+      <c r="P84">
+        <v>1203.0938120000001</v>
+      </c>
+      <c r="Q84">
+        <v>201</v>
+      </c>
+      <c r="S84">
+        <v>23.99005</v>
+      </c>
+      <c r="T84">
+        <v>5.0149699999999999</v>
+      </c>
+      <c r="U84">
+        <v>219</v>
+      </c>
+      <c r="V84">
+        <v>5.4640719999999998</v>
+      </c>
+      <c r="W84">
+        <v>22.018265</v>
+      </c>
+      <c r="X84">
+        <v>176</v>
+      </c>
+      <c r="Y84">
+        <v>27.397727</v>
+      </c>
+    </row>
+    <row r="85" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>25</v>
+      </c>
+      <c r="B85" t="s">
+        <v>26</v>
+      </c>
+      <c r="C85" t="s">
+        <v>154</v>
+      </c>
+      <c r="D85" t="s">
+        <v>38</v>
+      </c>
+      <c r="E85" t="s">
+        <v>29</v>
+      </c>
+      <c r="F85">
+        <v>350</v>
+      </c>
+      <c r="G85" t="s">
+        <v>39</v>
+      </c>
+      <c r="H85">
+        <v>5272</v>
+      </c>
+      <c r="I85">
+        <v>1.3753789999999999</v>
+      </c>
+      <c r="J85">
+        <v>13.75142857</v>
+      </c>
+      <c r="K85">
+        <v>160</v>
+      </c>
+      <c r="L85" t="s">
+        <v>30</v>
+      </c>
+      <c r="M85">
+        <v>4813</v>
+      </c>
+      <c r="N85" t="s">
+        <v>85</v>
+      </c>
+      <c r="O85">
+        <v>7251</v>
+      </c>
+      <c r="P85">
+        <v>663.77051400000005</v>
+      </c>
+      <c r="Q85">
+        <v>350</v>
+      </c>
+      <c r="S85">
+        <v>13.751429</v>
+      </c>
+      <c r="T85">
+        <v>4.8269200000000003</v>
+      </c>
+      <c r="U85">
+        <v>391</v>
+      </c>
+      <c r="V85">
+        <v>5.39236</v>
+      </c>
+      <c r="W85">
+        <v>12.309462999999999</v>
+      </c>
+      <c r="X85">
+        <v>287</v>
+      </c>
+      <c r="Y85">
+        <v>16.770035</v>
+      </c>
+    </row>
+    <row r="86" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>25</v>
+      </c>
+      <c r="B86" t="s">
+        <v>26</v>
+      </c>
+      <c r="C86" t="s">
+        <v>155</v>
+      </c>
+      <c r="D86" t="s">
+        <v>38</v>
+      </c>
+      <c r="E86" t="s">
+        <v>29</v>
+      </c>
+      <c r="F86">
+        <v>619</v>
+      </c>
+      <c r="G86" t="s">
+        <v>39</v>
+      </c>
+      <c r="H86">
+        <v>3764</v>
+      </c>
+      <c r="I86">
+        <v>1.3174809999999999</v>
+      </c>
+      <c r="J86">
+        <v>7.7512116300000002</v>
+      </c>
+      <c r="K86">
+        <v>160</v>
+      </c>
+      <c r="L86" t="s">
+        <v>30</v>
+      </c>
+      <c r="M86">
+        <v>4798</v>
+      </c>
+      <c r="N86" t="s">
+        <v>85</v>
+      </c>
+      <c r="O86">
+        <v>4959</v>
+      </c>
+      <c r="P86">
+        <v>967.53377699999999</v>
+      </c>
+      <c r="Q86">
+        <v>619</v>
+      </c>
+      <c r="S86">
+        <v>7.7512119999999998</v>
+      </c>
+      <c r="T86">
+        <v>12.482355</v>
+      </c>
+      <c r="U86">
+        <v>648</v>
+      </c>
+      <c r="V86">
+        <v>13.067151000000001</v>
+      </c>
+      <c r="W86">
+        <v>7.4043210000000004</v>
+      </c>
+      <c r="X86">
+        <v>522</v>
+      </c>
+      <c r="Y86">
+        <v>9.1915709999999997</v>
+      </c>
+    </row>
+    <row r="87" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>25</v>
+      </c>
+      <c r="B87" t="s">
+        <v>26</v>
+      </c>
+      <c r="C87" t="s">
+        <v>156</v>
+      </c>
+      <c r="D87" t="s">
+        <v>38</v>
+      </c>
+      <c r="E87" t="s">
+        <v>29</v>
+      </c>
+      <c r="F87">
+        <v>251</v>
+      </c>
+      <c r="G87" t="s">
+        <v>39</v>
+      </c>
+      <c r="H87">
+        <v>4616</v>
+      </c>
+      <c r="I87">
+        <v>1.147964</v>
+      </c>
+      <c r="J87">
+        <v>19.147410359999999</v>
+      </c>
+      <c r="K87">
+        <v>160</v>
+      </c>
+      <c r="L87" t="s">
+        <v>30</v>
+      </c>
+      <c r="M87">
+        <v>4806</v>
+      </c>
+      <c r="N87" t="s">
+        <v>85</v>
+      </c>
+      <c r="O87">
+        <v>5299</v>
+      </c>
+      <c r="P87">
+        <v>906.96357799999998</v>
+      </c>
+      <c r="Q87">
+        <v>251</v>
+      </c>
+      <c r="S87">
+        <v>19.147410000000001</v>
+      </c>
+      <c r="T87">
+        <v>4.7367429999999997</v>
+      </c>
+      <c r="U87">
+        <v>255</v>
+      </c>
+      <c r="V87">
+        <v>4.8122290000000003</v>
+      </c>
+      <c r="W87">
+        <v>18.847059000000002</v>
+      </c>
+      <c r="X87">
+        <v>96</v>
+      </c>
+      <c r="Y87">
+        <v>50.0625</v>
+      </c>
+    </row>
+    <row r="88" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>25</v>
+      </c>
+      <c r="B88" t="s">
+        <v>26</v>
+      </c>
+      <c r="C88" t="s">
+        <v>157</v>
+      </c>
+      <c r="D88" t="s">
+        <v>38</v>
+      </c>
+      <c r="E88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F88">
+        <v>385</v>
+      </c>
+      <c r="G88" t="s">
+        <v>39</v>
+      </c>
+      <c r="H88">
+        <v>4869</v>
+      </c>
+      <c r="I88">
+        <v>1.357979</v>
+      </c>
+      <c r="J88">
+        <v>12.55324675</v>
+      </c>
+      <c r="K88">
+        <v>160</v>
+      </c>
+      <c r="L88" t="s">
+        <v>30</v>
+      </c>
+      <c r="M88">
+        <v>4833</v>
+      </c>
+      <c r="N88" t="s">
+        <v>85</v>
+      </c>
+      <c r="O88">
+        <v>6612</v>
+      </c>
+      <c r="P88">
+        <v>730.94373900000005</v>
+      </c>
+      <c r="Q88">
+        <v>385</v>
+      </c>
+      <c r="S88">
+        <v>12.553247000000001</v>
+      </c>
+      <c r="T88">
+        <v>5.8227469999999997</v>
+      </c>
+      <c r="U88">
+        <v>436</v>
+      </c>
+      <c r="V88">
+        <v>6.5940709999999996</v>
+      </c>
+      <c r="W88">
+        <v>11.084861999999999</v>
+      </c>
+      <c r="X88">
+        <v>330</v>
+      </c>
+      <c r="Y88">
+        <v>14.645455</v>
+      </c>
+    </row>
+    <row r="89" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>25</v>
+      </c>
+      <c r="B89" t="s">
+        <v>26</v>
+      </c>
+      <c r="C89" t="s">
+        <v>158</v>
+      </c>
+      <c r="D89" t="s">
+        <v>38</v>
+      </c>
+      <c r="E89" t="s">
+        <v>29</v>
+      </c>
+      <c r="F89">
+        <v>149</v>
+      </c>
+      <c r="G89" t="s">
+        <v>39</v>
+      </c>
+      <c r="H89">
+        <v>2441</v>
+      </c>
+      <c r="I89">
+        <v>1.521917</v>
+      </c>
+      <c r="J89">
+        <v>32.228187920000003</v>
+      </c>
+      <c r="K89">
+        <v>160</v>
+      </c>
+      <c r="L89" t="s">
+        <v>30</v>
+      </c>
+      <c r="M89">
+        <v>4802</v>
+      </c>
+      <c r="N89" t="s">
+        <v>85</v>
+      </c>
+      <c r="O89">
+        <v>3715</v>
+      </c>
+      <c r="P89">
+        <v>1292.597577</v>
+      </c>
+      <c r="Q89">
+        <v>149</v>
+      </c>
+      <c r="S89">
+        <v>32.228188000000003</v>
+      </c>
+      <c r="T89">
+        <v>4.0107670000000004</v>
+      </c>
+      <c r="U89">
+        <v>162</v>
+      </c>
+      <c r="V89">
+        <v>4.3606999999999996</v>
+      </c>
+      <c r="W89">
+        <v>29.641974999999999</v>
+      </c>
+      <c r="X89">
+        <v>130</v>
+      </c>
+      <c r="Y89">
+        <v>36.938462000000001</v>
+      </c>
+    </row>
+    <row r="90" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>25</v>
+      </c>
+      <c r="B90" t="s">
+        <v>26</v>
+      </c>
+      <c r="C90" t="s">
+        <v>159</v>
+      </c>
+      <c r="D90" t="s">
+        <v>38</v>
+      </c>
+      <c r="E90" t="s">
+        <v>29</v>
+      </c>
+      <c r="F90">
+        <v>171</v>
+      </c>
+      <c r="G90" t="s">
+        <v>39</v>
+      </c>
+      <c r="H90">
+        <v>5413</v>
+      </c>
+      <c r="I90">
+        <v>1.2141139999999999</v>
+      </c>
+      <c r="J90">
+        <v>28.15789474</v>
+      </c>
+      <c r="K90">
+        <v>160</v>
+      </c>
+      <c r="L90" t="s">
+        <v>30</v>
+      </c>
+      <c r="M90">
+        <v>4815</v>
+      </c>
+      <c r="N90" t="s">
+        <v>85</v>
+      </c>
+      <c r="O90">
+        <v>6572</v>
+      </c>
+      <c r="P90">
+        <v>732.653682</v>
+      </c>
+      <c r="Q90">
+        <v>171</v>
+      </c>
+      <c r="S90">
+        <v>28.157895</v>
+      </c>
+      <c r="T90">
+        <v>2.6019480000000001</v>
+      </c>
+      <c r="U90">
+        <v>236</v>
+      </c>
+      <c r="V90">
+        <v>3.590992</v>
+      </c>
+      <c r="W90">
+        <v>20.402542</v>
+      </c>
+      <c r="X90">
+        <v>131</v>
+      </c>
+      <c r="Y90">
+        <v>36.755724999999998</v>
+      </c>
+    </row>
+    <row r="91" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>25</v>
+      </c>
+      <c r="B91" t="s">
+        <v>26</v>
+      </c>
+      <c r="C91" t="s">
+        <v>160</v>
+      </c>
+      <c r="D91" t="s">
+        <v>28</v>
+      </c>
+      <c r="E91" t="s">
+        <v>29</v>
+      </c>
+      <c r="F91">
+        <v>132</v>
+      </c>
+      <c r="G91" t="s">
+        <v>39</v>
+      </c>
+      <c r="H91">
+        <v>2788</v>
+      </c>
+      <c r="I91">
+        <v>1.4117649999999999</v>
+      </c>
+      <c r="J91">
+        <v>36.560606059999998</v>
+      </c>
+      <c r="K91">
+        <v>160</v>
+      </c>
+      <c r="L91" t="s">
+        <v>30</v>
+      </c>
+      <c r="M91">
+        <v>4826</v>
+      </c>
+      <c r="N91" t="s">
+        <v>85</v>
+      </c>
+      <c r="O91">
+        <v>3936</v>
+      </c>
+      <c r="P91">
+        <v>1226.117886</v>
+      </c>
+      <c r="Q91">
+        <v>132</v>
+      </c>
+      <c r="S91">
+        <v>36.560606</v>
+      </c>
+      <c r="T91">
+        <v>3.3536589999999999</v>
+      </c>
+      <c r="U91">
+        <v>148</v>
+      </c>
+      <c r="V91">
+        <v>3.7601629999999999</v>
+      </c>
+      <c r="W91">
+        <v>32.608108000000001</v>
+      </c>
+      <c r="X91">
+        <v>113</v>
+      </c>
+      <c r="Y91">
+        <v>42.707965000000002</v>
+      </c>
+    </row>
+    <row r="92" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>25</v>
+      </c>
+      <c r="B92" t="s">
+        <v>26</v>
+      </c>
+      <c r="C92" t="s">
+        <v>161</v>
+      </c>
+      <c r="D92" t="s">
+        <v>28</v>
+      </c>
+      <c r="E92" t="s">
+        <v>29</v>
+      </c>
+      <c r="F92">
+        <v>83</v>
+      </c>
+      <c r="G92" t="s">
+        <v>39</v>
+      </c>
+      <c r="H92">
+        <v>2507</v>
+      </c>
+      <c r="I92">
+        <v>1.258875</v>
+      </c>
+      <c r="J92">
+        <v>57.481927710000001</v>
+      </c>
+      <c r="K92">
+        <v>160</v>
+      </c>
+      <c r="L92" t="s">
+        <v>30</v>
+      </c>
+      <c r="M92">
+        <v>4771</v>
+      </c>
+      <c r="N92" t="s">
+        <v>85</v>
+      </c>
+      <c r="O92">
+        <v>3156</v>
+      </c>
+      <c r="P92">
+        <v>1511.7237009999999</v>
+      </c>
+      <c r="Q92">
+        <v>83</v>
+      </c>
+      <c r="S92">
+        <v>57.481928000000003</v>
+      </c>
+      <c r="T92">
+        <v>2.6299109999999999</v>
+      </c>
+      <c r="U92">
+        <v>87</v>
+      </c>
+      <c r="V92">
+        <v>2.7566540000000002</v>
+      </c>
+      <c r="W92">
+        <v>54.839080000000003</v>
+      </c>
+      <c r="X92">
+        <v>53</v>
+      </c>
+      <c r="Y92">
+        <v>90.018867999999998</v>
+      </c>
+    </row>
+    <row r="93" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>25</v>
+      </c>
+      <c r="B93" t="s">
+        <v>26</v>
+      </c>
+      <c r="C93" t="s">
+        <v>162</v>
+      </c>
+      <c r="D93" t="s">
+        <v>38</v>
+      </c>
+      <c r="E93" t="s">
+        <v>29</v>
+      </c>
+      <c r="F93">
+        <v>103</v>
+      </c>
+      <c r="G93" t="s">
+        <v>39</v>
+      </c>
+      <c r="H93">
+        <v>2616</v>
+      </c>
+      <c r="I93">
+        <v>1.3180430000000001</v>
+      </c>
+      <c r="J93">
+        <v>46.902912620000002</v>
+      </c>
+      <c r="K93">
+        <v>160</v>
+      </c>
+      <c r="L93" t="s">
+        <v>30</v>
+      </c>
+      <c r="M93">
+        <v>4831</v>
+      </c>
+      <c r="N93" t="s">
+        <v>85</v>
+      </c>
+      <c r="O93">
+        <v>3448</v>
+      </c>
+      <c r="P93">
+        <v>1401.1020880000001</v>
+      </c>
+      <c r="Q93">
+        <v>103</v>
+      </c>
+      <c r="S93">
+        <v>46.902912999999998</v>
+      </c>
+      <c r="T93">
+        <v>2.9872390000000002</v>
+      </c>
+      <c r="U93">
+        <v>111</v>
+      </c>
+      <c r="V93">
+        <v>3.219258</v>
+      </c>
+      <c r="W93">
+        <v>43.522523</v>
+      </c>
+      <c r="X93">
+        <v>78</v>
+      </c>
+      <c r="Y93">
+        <v>61.935896999999997</v>
+      </c>
+    </row>
+    <row r="94" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>25</v>
+      </c>
+      <c r="B94" t="s">
+        <v>26</v>
+      </c>
+      <c r="C94" t="s">
+        <v>163</v>
+      </c>
+      <c r="D94" t="s">
+        <v>38</v>
+      </c>
+      <c r="E94" t="s">
+        <v>29</v>
+      </c>
+      <c r="F94">
+        <v>118</v>
+      </c>
+      <c r="G94" t="s">
+        <v>39</v>
+      </c>
+      <c r="H94">
+        <v>2545</v>
+      </c>
+      <c r="I94">
+        <v>1.3033399999999999</v>
+      </c>
+      <c r="J94">
+        <v>40.694915250000001</v>
+      </c>
+      <c r="K94">
+        <v>160</v>
+      </c>
+      <c r="L94" t="s">
+        <v>30</v>
+      </c>
+      <c r="M94">
+        <v>4802</v>
+      </c>
+      <c r="N94" t="s">
+        <v>85</v>
+      </c>
+      <c r="O94">
+        <v>3317</v>
+      </c>
+      <c r="P94">
+        <v>1447.6936989999999</v>
+      </c>
+      <c r="Q94">
+        <v>118</v>
+      </c>
+      <c r="S94">
+        <v>40.694915000000002</v>
+      </c>
+      <c r="T94">
+        <v>3.5574309999999998</v>
+      </c>
+      <c r="U94">
+        <v>124</v>
+      </c>
+      <c r="V94">
+        <v>3.738318</v>
+      </c>
+      <c r="W94">
+        <v>38.725805999999999</v>
+      </c>
+      <c r="X94">
+        <v>99</v>
+      </c>
+      <c r="Y94">
+        <v>48.505051000000002</v>
+      </c>
+    </row>
+    <row r="95" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>25</v>
+      </c>
+      <c r="B95" t="s">
+        <v>26</v>
+      </c>
+      <c r="C95" t="s">
+        <v>164</v>
+      </c>
+      <c r="D95" t="s">
+        <v>38</v>
+      </c>
+      <c r="E95" t="s">
+        <v>29</v>
+      </c>
+      <c r="F95">
+        <v>152</v>
+      </c>
+      <c r="G95" t="s">
+        <v>39</v>
+      </c>
+      <c r="H95">
+        <v>3360</v>
+      </c>
+      <c r="I95">
+        <v>1.5809519999999999</v>
+      </c>
+      <c r="J95">
+        <v>31.625</v>
+      </c>
+      <c r="K95">
+        <v>160</v>
+      </c>
+      <c r="L95" t="s">
+        <v>30</v>
+      </c>
+      <c r="M95">
+        <v>4807</v>
+      </c>
+      <c r="N95" t="s">
+        <v>85</v>
+      </c>
+      <c r="O95">
+        <v>5312</v>
+      </c>
+      <c r="P95">
+        <v>904.93222900000001</v>
+      </c>
+      <c r="Q95">
+        <v>152</v>
+      </c>
+      <c r="S95">
+        <v>31.625</v>
+      </c>
+      <c r="T95">
+        <v>2.8614459999999999</v>
+      </c>
+      <c r="U95">
+        <v>166</v>
+      </c>
+      <c r="V95">
+        <v>3.125</v>
+      </c>
+      <c r="W95">
+        <v>28.957830999999999</v>
+      </c>
+      <c r="X95">
+        <v>133</v>
+      </c>
+      <c r="Y95">
+        <v>36.142856999999999</v>
+      </c>
+    </row>
+    <row r="96" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>25</v>
+      </c>
+      <c r="B96" t="s">
+        <v>26</v>
+      </c>
+      <c r="C96" t="s">
+        <v>165</v>
+      </c>
+      <c r="D96" t="s">
+        <v>38</v>
+      </c>
+      <c r="E96" t="s">
+        <v>29</v>
+      </c>
+      <c r="F96">
+        <v>116</v>
+      </c>
+      <c r="G96" t="s">
+        <v>39</v>
+      </c>
+      <c r="H96">
+        <v>4541</v>
+      </c>
+      <c r="I96">
+        <v>1.3695219999999999</v>
+      </c>
+      <c r="J96">
+        <v>41.456896550000003</v>
+      </c>
+      <c r="K96">
+        <v>160</v>
+      </c>
+      <c r="L96" t="s">
+        <v>30</v>
+      </c>
+      <c r="M96">
+        <v>4809</v>
+      </c>
+      <c r="N96" t="s">
+        <v>85</v>
+      </c>
+      <c r="O96">
+        <v>6219</v>
+      </c>
+      <c r="P96">
+        <v>773.27544599999999</v>
+      </c>
+      <c r="Q96">
+        <v>116</v>
+      </c>
+      <c r="S96">
+        <v>41.456896999999998</v>
+      </c>
+      <c r="T96">
+        <v>1.8652519999999999</v>
+      </c>
+      <c r="U96">
+        <v>146</v>
+      </c>
+      <c r="V96">
+        <v>2.3476439999999998</v>
+      </c>
+      <c r="W96">
+        <v>32.938355999999999</v>
+      </c>
+      <c r="X96">
+        <v>96</v>
+      </c>
+      <c r="Y96">
+        <v>50.09375</v>
+      </c>
+    </row>
+    <row r="97" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>25</v>
+      </c>
+      <c r="B97" t="s">
+        <v>26</v>
+      </c>
+      <c r="C97" t="s">
+        <v>166</v>
+      </c>
+      <c r="D97" t="s">
+        <v>38</v>
+      </c>
+      <c r="E97" t="s">
+        <v>29</v>
+      </c>
+      <c r="F97">
+        <v>192</v>
+      </c>
+      <c r="G97" t="s">
+        <v>39</v>
+      </c>
+      <c r="H97">
+        <v>2641</v>
+      </c>
+      <c r="I97">
+        <v>1.4982960000000001</v>
+      </c>
+      <c r="J97">
+        <v>24.916666670000001</v>
+      </c>
+      <c r="K97">
+        <v>160</v>
+      </c>
+      <c r="L97" t="s">
+        <v>30</v>
+      </c>
+      <c r="M97">
+        <v>4784</v>
+      </c>
+      <c r="N97" t="s">
+        <v>167</v>
+      </c>
+      <c r="O97">
+        <v>3957</v>
+      </c>
+      <c r="P97">
+        <v>1208.996715</v>
+      </c>
+      <c r="Q97">
+        <v>192</v>
+      </c>
+      <c r="S97">
+        <v>24.916667</v>
+      </c>
+      <c r="T97">
+        <v>4.8521609999999997</v>
+      </c>
+      <c r="U97">
+        <v>203</v>
+      </c>
+      <c r="V97">
+        <v>5.1301490000000003</v>
+      </c>
+      <c r="W97">
+        <v>23.566502</v>
+      </c>
+      <c r="X97">
+        <v>11</v>
+      </c>
+      <c r="Y97">
+        <v>434.90909099999999</v>
+      </c>
+    </row>
+    <row r="98" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>25</v>
+      </c>
+      <c r="B98" t="s">
+        <v>26</v>
+      </c>
+      <c r="C98" t="s">
+        <v>168</v>
+      </c>
+      <c r="D98" t="s">
+        <v>38</v>
+      </c>
+      <c r="E98" t="s">
+        <v>29</v>
+      </c>
+      <c r="F98">
+        <v>274</v>
+      </c>
+      <c r="G98" t="s">
+        <v>39</v>
+      </c>
+      <c r="H98">
+        <v>3607</v>
+      </c>
+      <c r="I98">
+        <v>1.4981979999999999</v>
+      </c>
+      <c r="J98">
+        <v>17.306569339999999</v>
+      </c>
+      <c r="K98">
+        <v>160</v>
+      </c>
+      <c r="L98" t="s">
+        <v>30</v>
+      </c>
+      <c r="M98">
+        <v>4742</v>
+      </c>
+      <c r="N98" t="s">
+        <v>167</v>
+      </c>
+      <c r="O98">
+        <v>5404</v>
+      </c>
+      <c r="P98">
+        <v>877.49815000000001</v>
+      </c>
+      <c r="Q98">
+        <v>274</v>
+      </c>
+      <c r="S98">
+        <v>17.306569</v>
+      </c>
+      <c r="T98">
+        <v>5.0703180000000003</v>
+      </c>
+      <c r="U98">
+        <v>296</v>
+      </c>
+      <c r="V98">
+        <v>5.4774240000000001</v>
+      </c>
+      <c r="W98">
+        <v>16.02027</v>
+      </c>
+      <c r="X98">
+        <v>19</v>
+      </c>
+      <c r="Y98">
+        <v>249.578947</v>
+      </c>
+    </row>
+    <row r="99" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>25</v>
+      </c>
+      <c r="B99" t="s">
+        <v>26</v>
+      </c>
+      <c r="C99" t="s">
+        <v>169</v>
+      </c>
+      <c r="D99" t="s">
+        <v>38</v>
+      </c>
+      <c r="E99" t="s">
+        <v>29</v>
+      </c>
+      <c r="F99">
+        <v>196</v>
+      </c>
+      <c r="G99" t="s">
+        <v>39</v>
+      </c>
+      <c r="H99">
+        <v>4560</v>
+      </c>
+      <c r="I99">
+        <v>1.320614</v>
+      </c>
+      <c r="J99">
+        <v>24.474489800000001</v>
+      </c>
+      <c r="K99">
+        <v>160</v>
+      </c>
+      <c r="L99" t="s">
+        <v>30</v>
+      </c>
+      <c r="M99">
+        <v>4797</v>
+      </c>
+      <c r="N99" t="s">
+        <v>167</v>
+      </c>
+      <c r="O99">
+        <v>6022</v>
+      </c>
+      <c r="P99">
+        <v>796.57920999999999</v>
+      </c>
+      <c r="Q99">
+        <v>196</v>
+      </c>
+      <c r="S99">
+        <v>24.474489999999999</v>
+      </c>
+      <c r="T99">
+        <v>3.2547329999999999</v>
+      </c>
+      <c r="U99">
+        <v>245</v>
+      </c>
+      <c r="V99">
+        <v>4.068416</v>
+      </c>
+      <c r="W99">
+        <v>19.579592000000002</v>
+      </c>
+      <c r="X99">
+        <v>33</v>
+      </c>
+      <c r="Y99">
+        <v>145.36363600000001</v>
+      </c>
+    </row>
+    <row r="100" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>25</v>
+      </c>
+      <c r="B100" t="s">
+        <v>26</v>
+      </c>
+      <c r="C100" t="s">
+        <v>170</v>
+      </c>
+      <c r="D100" t="s">
+        <v>68</v>
+      </c>
+      <c r="E100" t="s">
+        <v>29</v>
+      </c>
+      <c r="F100">
+        <v>81</v>
+      </c>
+      <c r="G100" t="s">
+        <v>39</v>
+      </c>
+      <c r="H100">
+        <v>2656</v>
+      </c>
+      <c r="I100">
+        <v>1.724774</v>
+      </c>
+      <c r="J100">
+        <v>59.172839510000003</v>
+      </c>
+      <c r="K100">
+        <v>160</v>
+      </c>
+      <c r="L100" t="s">
+        <v>30</v>
+      </c>
+      <c r="M100">
+        <v>4793</v>
+      </c>
+      <c r="N100" t="s">
+        <v>171</v>
+      </c>
+      <c r="O100">
+        <v>4581</v>
+      </c>
+      <c r="P100">
+        <v>1046.2781050000001</v>
+      </c>
+      <c r="Q100">
+        <v>81</v>
+      </c>
+      <c r="S100">
+        <v>59.172840000000001</v>
+      </c>
+      <c r="T100">
+        <v>1.768173</v>
+      </c>
+      <c r="U100">
+        <v>102</v>
+      </c>
+      <c r="V100">
+        <v>2.226588</v>
+      </c>
+      <c r="W100">
+        <v>46.990195999999997</v>
+      </c>
+      <c r="X100">
+        <v>61</v>
+      </c>
+      <c r="Y100">
+        <v>78.573769999999996</v>
+      </c>
+    </row>
+    <row r="101" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>25</v>
+      </c>
+      <c r="B101" t="s">
+        <v>26</v>
+      </c>
+      <c r="C101" t="s">
+        <v>172</v>
+      </c>
+      <c r="D101" t="s">
+        <v>28</v>
+      </c>
+      <c r="E101" t="s">
+        <v>29</v>
+      </c>
+      <c r="F101">
+        <v>99</v>
+      </c>
+      <c r="G101" t="s">
+        <v>39</v>
+      </c>
+      <c r="H101">
+        <v>2347</v>
+      </c>
+      <c r="I101">
+        <v>1.253941</v>
+      </c>
+      <c r="J101">
+        <v>48.858585859999998</v>
+      </c>
+      <c r="K101">
+        <v>160</v>
+      </c>
+      <c r="L101" t="s">
+        <v>30</v>
+      </c>
+      <c r="M101">
+        <v>4837</v>
+      </c>
+      <c r="N101" t="s">
+        <v>98</v>
+      </c>
+      <c r="O101">
+        <v>2943</v>
+      </c>
+      <c r="P101">
+        <v>1643.5609919999999</v>
+      </c>
+      <c r="Q101">
+        <v>99</v>
+      </c>
+      <c r="S101">
+        <v>48.858586000000003</v>
+      </c>
+      <c r="T101">
+        <v>3.3639139999999998</v>
+      </c>
+      <c r="U101">
+        <v>101</v>
+      </c>
+      <c r="V101">
+        <v>3.4318719999999998</v>
+      </c>
+      <c r="W101">
+        <v>47.891089000000001</v>
+      </c>
+      <c r="X101">
+        <v>61</v>
+      </c>
+      <c r="Y101">
+        <v>79.295081999999994</v>
+      </c>
+    </row>
+    <row r="102" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>25</v>
+      </c>
+      <c r="B102" t="s">
+        <v>26</v>
+      </c>
+      <c r="C102" t="s">
+        <v>173</v>
+      </c>
+      <c r="D102" t="s">
+        <v>38</v>
+      </c>
+      <c r="E102" t="s">
+        <v>29</v>
+      </c>
+      <c r="F102">
+        <v>130</v>
+      </c>
+      <c r="G102" t="s">
+        <v>39</v>
+      </c>
+      <c r="H102">
+        <v>2382</v>
+      </c>
+      <c r="I102">
+        <v>1.8224180000000001</v>
+      </c>
+      <c r="J102">
+        <v>32.776923080000003</v>
+      </c>
+      <c r="K102">
+        <v>160</v>
+      </c>
+      <c r="L102" t="s">
+        <v>30</v>
+      </c>
+      <c r="M102">
+        <v>4261</v>
+      </c>
+      <c r="N102" t="s">
+        <v>95</v>
+      </c>
+      <c r="O102">
+        <v>4341</v>
+      </c>
+      <c r="P102">
+        <v>981.57106699999997</v>
+      </c>
+      <c r="Q102">
+        <v>130</v>
+      </c>
+      <c r="S102">
+        <v>32.776922999999996</v>
+      </c>
+      <c r="T102">
+        <v>2.9947020000000002</v>
+      </c>
+      <c r="U102">
+        <v>161</v>
+      </c>
+      <c r="V102">
+        <v>3.7088230000000002</v>
+      </c>
+      <c r="W102">
+        <v>26.465838999999999</v>
+      </c>
+      <c r="X102">
+        <v>124</v>
+      </c>
+      <c r="Y102">
+        <v>34.362903000000003</v>
+      </c>
+    </row>
+    <row r="103" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>25</v>
+      </c>
+      <c r="B103" t="s">
+        <v>26</v>
+      </c>
+      <c r="C103" t="s">
+        <v>174</v>
+      </c>
+      <c r="D103" t="s">
+        <v>38</v>
+      </c>
+      <c r="E103" t="s">
+        <v>29</v>
+      </c>
+      <c r="F103">
+        <v>172</v>
+      </c>
+      <c r="G103" t="s">
+        <v>39</v>
+      </c>
+      <c r="H103">
+        <v>2715</v>
+      </c>
+      <c r="I103">
+        <v>1.5034989999999999</v>
+      </c>
+      <c r="J103">
+        <v>24.808139529999998</v>
+      </c>
+      <c r="K103">
+        <v>160</v>
+      </c>
+      <c r="L103" t="s">
+        <v>30</v>
+      </c>
+      <c r="M103">
+        <v>4267</v>
+      </c>
+      <c r="N103" t="s">
+        <v>95</v>
+      </c>
+      <c r="O103">
+        <v>4082</v>
+      </c>
+      <c r="P103">
+        <v>1045.320921</v>
+      </c>
+      <c r="Q103">
+        <v>172</v>
+      </c>
+      <c r="S103">
+        <v>24.808140000000002</v>
+      </c>
+      <c r="T103">
+        <v>4.2136209999999998</v>
+      </c>
+      <c r="U103">
+        <v>190</v>
+      </c>
+      <c r="V103">
+        <v>4.6545810000000003</v>
+      </c>
+      <c r="W103">
+        <v>22.457895000000001</v>
+      </c>
+      <c r="X103">
+        <v>150</v>
+      </c>
+      <c r="Y103">
+        <v>28.446667000000001</v>
+      </c>
+    </row>
+    <row r="104" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>25</v>
+      </c>
+      <c r="B104" t="s">
+        <v>26</v>
+      </c>
+      <c r="C104" t="s">
+        <v>175</v>
+      </c>
+      <c r="D104" t="s">
+        <v>38</v>
+      </c>
+      <c r="E104" t="s">
+        <v>29</v>
+      </c>
+      <c r="F104">
+        <v>82</v>
+      </c>
+      <c r="G104" t="s">
+        <v>39</v>
+      </c>
+      <c r="H104">
+        <v>2659</v>
+      </c>
+      <c r="I104">
+        <v>1.503949</v>
+      </c>
+      <c r="J104">
+        <v>52.036585369999997</v>
+      </c>
+      <c r="K104">
+        <v>160</v>
+      </c>
+      <c r="L104" t="s">
+        <v>30</v>
+      </c>
+      <c r="M104">
+        <v>4267</v>
+      </c>
+      <c r="N104" t="s">
+        <v>95</v>
+      </c>
+      <c r="O104">
+        <v>3999</v>
+      </c>
+      <c r="P104">
+        <v>1067.016754</v>
+      </c>
+      <c r="Q104">
+        <v>82</v>
+      </c>
+      <c r="S104">
+        <v>52.036585000000002</v>
+      </c>
+      <c r="T104">
+        <v>2.050513</v>
+      </c>
+      <c r="U104">
+        <v>97</v>
+      </c>
+      <c r="V104">
+        <v>2.4256060000000002</v>
+      </c>
+      <c r="W104">
+        <v>43.989691000000001</v>
+      </c>
+      <c r="X104">
+        <v>77</v>
+      </c>
+      <c r="Y104">
+        <v>55.415584000000003</v>
+      </c>
+    </row>
+    <row r="105" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>25</v>
+      </c>
+      <c r="B105" t="s">
+        <v>26</v>
+      </c>
+      <c r="C105" t="s">
+        <v>176</v>
+      </c>
+      <c r="D105" t="s">
+        <v>38</v>
+      </c>
+      <c r="E105" t="s">
+        <v>29</v>
+      </c>
+      <c r="F105">
+        <v>247</v>
+      </c>
+      <c r="G105" t="s">
+        <v>39</v>
+      </c>
+      <c r="H105">
+        <v>3324</v>
+      </c>
+      <c r="I105">
+        <v>1.481047</v>
+      </c>
+      <c r="J105">
+        <v>17.299595140000001</v>
+      </c>
+      <c r="K105">
+        <v>160</v>
+      </c>
+      <c r="L105" t="s">
+        <v>30</v>
+      </c>
+      <c r="M105">
+        <v>4273</v>
+      </c>
+      <c r="N105" t="s">
+        <v>95</v>
+      </c>
+      <c r="O105">
+        <v>4923</v>
+      </c>
+      <c r="P105">
+        <v>867.96668699999998</v>
+      </c>
+      <c r="Q105">
+        <v>247</v>
+      </c>
+      <c r="S105">
+        <v>17.299595</v>
+      </c>
+      <c r="T105">
+        <v>5.0172660000000002</v>
+      </c>
+      <c r="U105">
+        <v>276</v>
+      </c>
+      <c r="V105">
+        <v>5.606338</v>
+      </c>
+      <c r="W105">
+        <v>15.481884000000001</v>
+      </c>
+      <c r="X105">
+        <v>13</v>
+      </c>
+      <c r="Y105">
+        <v>328.69230800000003</v>
+      </c>
+    </row>
+    <row r="106" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>25</v>
+      </c>
+      <c r="B106" t="s">
+        <v>26</v>
+      </c>
+      <c r="C106" t="s">
+        <v>177</v>
+      </c>
+      <c r="D106" t="s">
+        <v>38</v>
+      </c>
+      <c r="E106" t="s">
+        <v>29</v>
+      </c>
+      <c r="F106">
+        <v>154</v>
+      </c>
+      <c r="G106" t="s">
+        <v>39</v>
+      </c>
+      <c r="H106">
+        <v>2518</v>
+      </c>
+      <c r="I106">
+        <v>1.545671</v>
+      </c>
+      <c r="J106">
+        <v>27.714285709999999</v>
+      </c>
+      <c r="K106">
+        <v>160</v>
+      </c>
+      <c r="L106" t="s">
+        <v>30</v>
+      </c>
+      <c r="M106">
+        <v>4268</v>
+      </c>
+      <c r="N106" t="s">
+        <v>95</v>
+      </c>
+      <c r="O106">
+        <v>3892</v>
+      </c>
+      <c r="P106">
+        <v>1096.608428</v>
+      </c>
+      <c r="Q106">
+        <v>154</v>
+      </c>
+      <c r="S106">
+        <v>27.714286000000001</v>
+      </c>
+      <c r="T106">
+        <v>3.9568349999999999</v>
+      </c>
+      <c r="U106">
+        <v>172</v>
+      </c>
+      <c r="V106">
+        <v>4.4193220000000002</v>
+      </c>
+      <c r="W106">
+        <v>24.813953000000001</v>
+      </c>
+      <c r="X106">
+        <v>129</v>
+      </c>
+      <c r="Y106">
+        <v>33.085270999999999</v>
+      </c>
+    </row>
+    <row r="107" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>25</v>
+      </c>
+      <c r="B107" t="s">
+        <v>26</v>
+      </c>
+      <c r="C107" t="s">
+        <v>178</v>
+      </c>
+      <c r="D107" t="s">
+        <v>38</v>
+      </c>
+      <c r="E107" t="s">
+        <v>29</v>
+      </c>
+      <c r="F107">
+        <v>178</v>
+      </c>
+      <c r="G107" t="s">
+        <v>39</v>
+      </c>
+      <c r="H107">
+        <v>3672</v>
+      </c>
+      <c r="I107">
+        <v>1.6236379999999999</v>
+      </c>
+      <c r="J107">
+        <v>23.943820219999999</v>
+      </c>
+      <c r="K107">
+        <v>160</v>
+      </c>
+      <c r="L107" t="s">
+        <v>30</v>
+      </c>
+      <c r="M107">
+        <v>4262</v>
+      </c>
+      <c r="N107" t="s">
+        <v>95</v>
+      </c>
+      <c r="O107">
+        <v>5962</v>
+      </c>
+      <c r="P107">
+        <v>714.86078499999996</v>
+      </c>
+      <c r="Q107">
+        <v>178</v>
+      </c>
+      <c r="S107">
+        <v>23.943819999999999</v>
+      </c>
+      <c r="T107">
+        <v>2.9855749999999999</v>
+      </c>
+      <c r="U107">
+        <v>234</v>
+      </c>
+      <c r="V107">
+        <v>3.9248569999999998</v>
+      </c>
+      <c r="W107">
+        <v>18.213674999999999</v>
+      </c>
+      <c r="X107">
+        <v>23</v>
+      </c>
+      <c r="Y107">
+        <v>185.304348</v>
+      </c>
+    </row>
+    <row r="108" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>25</v>
+      </c>
+      <c r="B108" t="s">
+        <v>26</v>
+      </c>
+      <c r="C108" t="s">
+        <v>179</v>
+      </c>
+      <c r="D108" t="s">
+        <v>38</v>
+      </c>
+      <c r="E108" t="s">
+        <v>29</v>
+      </c>
+      <c r="F108">
+        <v>126</v>
+      </c>
+      <c r="G108" t="s">
+        <v>39</v>
+      </c>
+      <c r="H108">
+        <v>3113</v>
+      </c>
+      <c r="I108">
+        <v>1.4400900000000001</v>
+      </c>
+      <c r="J108">
+        <v>33.730158729999999</v>
+      </c>
+      <c r="K108">
+        <v>160</v>
+      </c>
+      <c r="L108" t="s">
+        <v>30</v>
+      </c>
+      <c r="M108">
+        <v>4250</v>
+      </c>
+      <c r="N108" t="s">
+        <v>95</v>
+      </c>
+      <c r="O108">
+        <v>4483</v>
+      </c>
+      <c r="P108">
+        <v>948.02587600000004</v>
+      </c>
+      <c r="Q108">
+        <v>126</v>
+      </c>
+      <c r="S108">
+        <v>33.730159</v>
+      </c>
+      <c r="T108">
+        <v>2.8106179999999998</v>
+      </c>
+      <c r="U108">
+        <v>157</v>
+      </c>
+      <c r="V108">
+        <v>3.502119</v>
+      </c>
+      <c r="W108">
+        <v>27.070063999999999</v>
+      </c>
+      <c r="X108">
+        <v>97</v>
+      </c>
+      <c r="Y108">
+        <v>43.814433000000001</v>
+      </c>
+    </row>
+    <row r="109" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>25</v>
+      </c>
+      <c r="B109" t="s">
+        <v>26</v>
+      </c>
+      <c r="C109" t="s">
+        <v>180</v>
+      </c>
+      <c r="D109" t="s">
+        <v>38</v>
+      </c>
+      <c r="E109" t="s">
+        <v>29</v>
+      </c>
+      <c r="F109">
+        <v>85</v>
+      </c>
+      <c r="G109" t="s">
+        <v>39</v>
+      </c>
+      <c r="H109">
+        <v>2033</v>
+      </c>
+      <c r="I109">
+        <v>1.66306</v>
+      </c>
+      <c r="J109">
+        <v>50.141176469999998</v>
+      </c>
+      <c r="K109">
+        <v>160</v>
+      </c>
+      <c r="L109" t="s">
+        <v>30</v>
+      </c>
+      <c r="M109">
+        <v>4262</v>
+      </c>
+      <c r="N109" t="s">
+        <v>95</v>
+      </c>
+      <c r="O109">
+        <v>3381</v>
+      </c>
+      <c r="P109">
+        <v>1260.573795</v>
+      </c>
+      <c r="Q109">
+        <v>85</v>
+      </c>
+      <c r="S109">
+        <v>50.141176000000002</v>
+      </c>
+      <c r="T109">
+        <v>2.514049</v>
+      </c>
+      <c r="U109">
+        <v>100</v>
+      </c>
+      <c r="V109">
+        <v>2.9577049999999998</v>
+      </c>
+      <c r="W109">
+        <v>42.62</v>
+      </c>
+      <c r="X109">
+        <v>71</v>
+      </c>
+      <c r="Y109">
+        <v>60.028168999999998</v>
+      </c>
+    </row>
+    <row r="110" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>25</v>
+      </c>
+      <c r="B110" t="s">
+        <v>26</v>
+      </c>
+      <c r="C110" t="s">
+        <v>181</v>
+      </c>
+      <c r="D110" t="s">
+        <v>38</v>
+      </c>
+      <c r="E110" t="s">
+        <v>29</v>
+      </c>
+      <c r="F110">
+        <v>48</v>
+      </c>
+      <c r="G110" t="s">
+        <v>39</v>
+      </c>
+      <c r="H110">
+        <v>3672</v>
+      </c>
+      <c r="I110">
+        <v>1.5255989999999999</v>
+      </c>
+      <c r="J110">
+        <v>88.541666669999998</v>
+      </c>
+      <c r="K110">
+        <v>160</v>
+      </c>
+      <c r="L110" t="s">
+        <v>30</v>
+      </c>
+      <c r="M110">
+        <v>4250</v>
+      </c>
+      <c r="N110" t="s">
+        <v>95</v>
+      </c>
+      <c r="O110">
+        <v>5602</v>
+      </c>
+      <c r="P110">
+        <v>758.65762199999995</v>
+      </c>
+      <c r="Q110">
+        <v>48</v>
+      </c>
+      <c r="S110">
+        <v>88.541667000000004</v>
+      </c>
+      <c r="T110">
+        <v>0.85683699999999996</v>
+      </c>
+      <c r="U110">
+        <v>55</v>
+      </c>
+      <c r="V110">
+        <v>0.981792</v>
+      </c>
+      <c r="W110">
+        <v>77.272727000000003</v>
+      </c>
+      <c r="X110">
+        <v>36</v>
+      </c>
+      <c r="Y110">
+        <v>118.055556</v>
+      </c>
+    </row>
+    <row r="111" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>25</v>
+      </c>
+      <c r="B111" t="s">
+        <v>26</v>
+      </c>
+      <c r="C111" t="s">
+        <v>182</v>
+      </c>
+      <c r="D111" t="s">
+        <v>38</v>
+      </c>
+      <c r="E111" t="s">
+        <v>29</v>
+      </c>
+      <c r="F111">
+        <v>213</v>
+      </c>
+      <c r="G111" t="s">
+        <v>39</v>
+      </c>
+      <c r="H111">
+        <v>3412</v>
+      </c>
+      <c r="I111">
+        <v>1.4396249999999999</v>
+      </c>
+      <c r="J111">
+        <v>19.957746480000001</v>
+      </c>
+      <c r="K111">
+        <v>160</v>
+      </c>
+      <c r="L111" t="s">
+        <v>30</v>
+      </c>
+      <c r="M111">
+        <v>4251</v>
+      </c>
+      <c r="N111" t="s">
+        <v>95</v>
+      </c>
+      <c r="O111">
+        <v>4912</v>
+      </c>
+      <c r="P111">
+        <v>865.43159600000001</v>
+      </c>
+      <c r="Q111">
+        <v>213</v>
+      </c>
+      <c r="S111">
+        <v>19.957746</v>
+      </c>
+      <c r="T111">
+        <v>4.3363189999999996</v>
+      </c>
+      <c r="U111">
+        <v>264</v>
+      </c>
+      <c r="V111">
+        <v>5.374593</v>
+      </c>
+      <c r="W111">
+        <v>16.102273</v>
+      </c>
+      <c r="X111">
+        <v>177</v>
+      </c>
+      <c r="Y111">
+        <v>24.016949</v>
+      </c>
+    </row>
+    <row r="112" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>25</v>
+      </c>
+      <c r="B112" t="s">
+        <v>26</v>
+      </c>
+      <c r="C112" t="s">
+        <v>183</v>
+      </c>
+      <c r="D112" t="s">
+        <v>38</v>
+      </c>
+      <c r="E112" t="s">
+        <v>29</v>
+      </c>
+      <c r="F112">
+        <v>182</v>
+      </c>
+      <c r="G112" t="s">
+        <v>39</v>
+      </c>
+      <c r="H112">
+        <v>4349</v>
+      </c>
+      <c r="I112">
+        <v>1.4426300000000001</v>
+      </c>
+      <c r="J112">
+        <v>23.379120879999999</v>
+      </c>
+      <c r="K112">
+        <v>160</v>
+      </c>
+      <c r="L112" t="s">
+        <v>30</v>
+      </c>
+      <c r="M112">
+        <v>4255</v>
+      </c>
+      <c r="N112" t="s">
+        <v>95</v>
+      </c>
+      <c r="O112">
+        <v>6274</v>
+      </c>
+      <c r="P112">
+        <v>678.19572800000003</v>
+      </c>
+      <c r="Q112">
+        <v>182</v>
+      </c>
+      <c r="S112">
+        <v>23.379121000000001</v>
+      </c>
+      <c r="T112">
+        <v>2.9008609999999999</v>
+      </c>
+      <c r="U112">
+        <v>237</v>
+      </c>
+      <c r="V112">
+        <v>3.7774939999999999</v>
+      </c>
+      <c r="W112">
+        <v>17.953586999999999</v>
+      </c>
+      <c r="X112">
+        <v>150</v>
+      </c>
+      <c r="Y112">
+        <v>28.366667</v>
+      </c>
+    </row>
+    <row r="113" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>25</v>
+      </c>
+      <c r="B113" t="s">
+        <v>26</v>
+      </c>
+      <c r="C113" t="s">
+        <v>184</v>
+      </c>
+      <c r="D113" t="s">
+        <v>38</v>
+      </c>
+      <c r="E113" t="s">
+        <v>29</v>
+      </c>
+      <c r="F113">
+        <v>240</v>
+      </c>
+      <c r="G113" t="s">
+        <v>39</v>
+      </c>
+      <c r="H113">
+        <v>3345</v>
+      </c>
+      <c r="I113">
+        <v>1.420628</v>
+      </c>
+      <c r="J113">
+        <v>17.795833330000001</v>
+      </c>
+      <c r="K113">
+        <v>160</v>
+      </c>
+      <c r="L113" t="s">
+        <v>30</v>
+      </c>
+      <c r="M113">
+        <v>4271</v>
+      </c>
+      <c r="N113" t="s">
+        <v>95</v>
+      </c>
+      <c r="O113">
+        <v>4752</v>
+      </c>
+      <c r="P113">
+        <v>898.77946099999997</v>
+      </c>
+      <c r="Q113">
+        <v>240</v>
+      </c>
+      <c r="S113">
+        <v>17.795832999999998</v>
+      </c>
+      <c r="T113">
+        <v>5.0505050000000002</v>
+      </c>
+      <c r="U113">
+        <v>277</v>
+      </c>
+      <c r="V113">
+        <v>5.8291250000000003</v>
+      </c>
+      <c r="W113">
+        <v>15.418773</v>
+      </c>
+      <c r="X113">
+        <v>202</v>
+      </c>
+      <c r="Y113">
+        <v>21.143564000000001</v>
+      </c>
+    </row>
+    <row r="114" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>25</v>
+      </c>
+      <c r="B114" t="s">
+        <v>26</v>
+      </c>
+      <c r="C114" t="s">
+        <v>185</v>
+      </c>
+      <c r="D114" t="s">
+        <v>38</v>
+      </c>
+      <c r="E114" t="s">
+        <v>29</v>
+      </c>
+      <c r="F114">
+        <v>370</v>
+      </c>
+      <c r="G114" t="s">
+        <v>39</v>
+      </c>
+      <c r="H114">
+        <v>3225</v>
+      </c>
+      <c r="I114">
+        <v>1.3556589999999999</v>
+      </c>
+      <c r="J114">
+        <v>11.47027027</v>
+      </c>
+      <c r="K114">
+        <v>160</v>
+      </c>
+      <c r="L114" t="s">
+        <v>30</v>
+      </c>
+      <c r="M114">
+        <v>4244</v>
+      </c>
+      <c r="N114" t="s">
+        <v>95</v>
+      </c>
+      <c r="O114">
+        <v>4372</v>
+      </c>
+      <c r="P114">
+        <v>970.72278100000005</v>
+      </c>
+      <c r="Q114">
+        <v>370</v>
+      </c>
+      <c r="S114">
+        <v>11.470269999999999</v>
+      </c>
+      <c r="T114">
+        <v>8.4629460000000005</v>
+      </c>
+      <c r="U114">
+        <v>421</v>
+      </c>
+      <c r="V114">
+        <v>9.6294599999999999</v>
+      </c>
+      <c r="W114">
+        <v>10.08076</v>
+      </c>
+      <c r="X114">
+        <v>334</v>
+      </c>
+      <c r="Y114">
+        <v>12.706587000000001</v>
+      </c>
+    </row>
+    <row r="115" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>25</v>
+      </c>
+      <c r="B115" t="s">
+        <v>26</v>
+      </c>
+      <c r="C115" t="s">
+        <v>186</v>
+      </c>
+      <c r="D115" t="s">
+        <v>38</v>
+      </c>
+      <c r="E115" t="s">
+        <v>29</v>
+      </c>
+      <c r="F115">
+        <v>519</v>
+      </c>
+      <c r="G115" t="s">
+        <v>39</v>
+      </c>
+      <c r="H115">
+        <v>4924</v>
+      </c>
+      <c r="I115">
+        <v>1.3458570000000001</v>
+      </c>
+      <c r="J115">
+        <v>8.1791907500000001</v>
+      </c>
+      <c r="K115">
+        <v>160</v>
+      </c>
+      <c r="L115" t="s">
+        <v>30</v>
+      </c>
+      <c r="M115">
+        <v>4245</v>
+      </c>
+      <c r="N115" t="s">
+        <v>95</v>
+      </c>
+      <c r="O115">
+        <v>6627</v>
+      </c>
+      <c r="P115">
+        <v>640.56133999999997</v>
+      </c>
+      <c r="Q115">
+        <v>519</v>
+      </c>
+      <c r="S115">
+        <v>8.1791909999999994</v>
+      </c>
+      <c r="T115">
+        <v>7.8315979999999996</v>
+      </c>
+      <c r="U115">
+        <v>562</v>
+      </c>
+      <c r="V115">
+        <v>8.4804589999999997</v>
+      </c>
+      <c r="W115">
+        <v>7.5533809999999999</v>
+      </c>
+      <c r="X115">
+        <v>417</v>
+      </c>
+      <c r="Y115">
+        <v>10.179855999999999</v>
+      </c>
+    </row>
+    <row r="116" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>25</v>
+      </c>
+      <c r="B116" t="s">
+        <v>26</v>
+      </c>
+      <c r="C116" t="s">
+        <v>187</v>
+      </c>
+      <c r="D116" t="s">
+        <v>38</v>
+      </c>
+      <c r="E116" t="s">
+        <v>29</v>
+      </c>
+      <c r="F116">
+        <v>211</v>
+      </c>
+      <c r="G116" t="s">
+        <v>39</v>
+      </c>
+      <c r="H116">
+        <v>3255</v>
+      </c>
+      <c r="I116">
+        <v>1.4906299999999999</v>
+      </c>
+      <c r="J116">
+        <v>20.042654030000001</v>
+      </c>
+      <c r="K116">
+        <v>160</v>
+      </c>
+      <c r="L116" t="s">
+        <v>30</v>
+      </c>
+      <c r="M116">
+        <v>4229</v>
+      </c>
+      <c r="N116" t="s">
+        <v>95</v>
+      </c>
+      <c r="O116">
+        <v>4852</v>
+      </c>
+      <c r="P116">
+        <v>871.59933999999998</v>
+      </c>
+      <c r="Q116">
+        <v>211</v>
+      </c>
+      <c r="S116">
+        <v>20.042653999999999</v>
+      </c>
+      <c r="T116">
+        <v>4.3487220000000004</v>
+      </c>
+      <c r="U116">
+        <v>257</v>
+      </c>
+      <c r="V116">
+        <v>5.2967849999999999</v>
+      </c>
+      <c r="W116">
+        <v>16.455252999999999</v>
+      </c>
+      <c r="X116">
+        <v>172</v>
+      </c>
+      <c r="Y116">
+        <v>24.587209000000001</v>
+      </c>
+    </row>
+    <row r="117" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>25</v>
+      </c>
+      <c r="B117" t="s">
+        <v>26</v>
+      </c>
+      <c r="C117" t="s">
+        <v>188</v>
+      </c>
+      <c r="D117" t="s">
+        <v>38</v>
+      </c>
+      <c r="E117" t="s">
+        <v>29</v>
+      </c>
+      <c r="F117">
+        <v>169</v>
+      </c>
+      <c r="G117" t="s">
+        <v>39</v>
+      </c>
+      <c r="H117">
+        <v>2477</v>
+      </c>
+      <c r="I117">
+        <v>1.656439</v>
+      </c>
+      <c r="J117">
+        <v>25.088757399999999</v>
+      </c>
+      <c r="K117">
+        <v>160</v>
+      </c>
+      <c r="L117" t="s">
+        <v>30</v>
+      </c>
+      <c r="M117">
+        <v>4240</v>
+      </c>
+      <c r="N117" t="s">
+        <v>95</v>
+      </c>
+      <c r="O117">
+        <v>4103</v>
+      </c>
+      <c r="P117">
+        <v>1033.390202</v>
+      </c>
+      <c r="Q117">
+        <v>169</v>
+      </c>
+      <c r="S117">
+        <v>25.088757000000001</v>
+      </c>
+      <c r="T117">
+        <v>4.1189369999999998</v>
+      </c>
+      <c r="U117">
+        <v>197</v>
+      </c>
+      <c r="V117">
+        <v>4.8013649999999997</v>
+      </c>
+      <c r="W117">
+        <v>21.522843000000002</v>
+      </c>
+      <c r="X117">
+        <v>146</v>
+      </c>
+      <c r="Y117">
+        <v>29.041096</v>
+      </c>
+    </row>
+    <row r="118" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>25</v>
+      </c>
+      <c r="B118" t="s">
+        <v>26</v>
+      </c>
+      <c r="C118" t="s">
+        <v>189</v>
+      </c>
+      <c r="D118" t="s">
+        <v>28</v>
+      </c>
+      <c r="E118" t="s">
+        <v>29</v>
+      </c>
+      <c r="H118">
+        <v>0</v>
+      </c>
+      <c r="I118">
+        <v>0</v>
+      </c>
+      <c r="K118">
+        <v>160</v>
+      </c>
+      <c r="L118" t="s">
+        <v>30</v>
+      </c>
+      <c r="M118">
+        <v>0</v>
+      </c>
+      <c r="N118" t="s">
+        <v>141</v>
+      </c>
+      <c r="O118">
+        <v>0</v>
+      </c>
+      <c r="P118">
+        <v>0</v>
+      </c>
+      <c r="U118">
+        <v>0</v>
+      </c>
+      <c r="V118">
+        <v>0</v>
+      </c>
+      <c r="W118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>25</v>
+      </c>
+      <c r="B119" t="s">
+        <v>26</v>
+      </c>
+      <c r="C119" t="s">
+        <v>140</v>
+      </c>
+      <c r="D119" t="s">
+        <v>28</v>
+      </c>
+      <c r="E119" t="s">
+        <v>29</v>
+      </c>
+      <c r="H119">
+        <v>0</v>
+      </c>
+      <c r="I119">
+        <v>0</v>
+      </c>
+      <c r="K119">
+        <v>160</v>
+      </c>
+      <c r="L119" t="s">
+        <v>30</v>
+      </c>
+      <c r="M119">
+        <v>0</v>
+      </c>
+      <c r="N119" t="s">
+        <v>141</v>
+      </c>
+      <c r="O119">
+        <v>0</v>
+      </c>
+      <c r="P119">
+        <v>0</v>
+      </c>
+      <c r="U119">
+        <v>0</v>
+      </c>
+      <c r="V119">
+        <v>0</v>
+      </c>
+      <c r="W119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>25</v>
+      </c>
+      <c r="B120" t="s">
+        <v>26</v>
+      </c>
+      <c r="C120" t="s">
+        <v>172</v>
+      </c>
+      <c r="D120" t="s">
+        <v>28</v>
+      </c>
+      <c r="E120" t="s">
+        <v>29</v>
+      </c>
+      <c r="H120">
+        <v>0</v>
+      </c>
+      <c r="I120">
+        <v>0</v>
+      </c>
+      <c r="K120">
+        <v>160</v>
+      </c>
+      <c r="L120" t="s">
+        <v>30</v>
+      </c>
+      <c r="M120">
+        <v>0</v>
+      </c>
+      <c r="N120" t="s">
+        <v>98</v>
+      </c>
+      <c r="O120">
+        <v>0</v>
+      </c>
+      <c r="P120">
+        <v>0</v>
+      </c>
+      <c r="U120">
+        <v>0</v>
+      </c>
+      <c r="V120">
+        <v>0</v>
+      </c>
+      <c r="W120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>25</v>
+      </c>
+      <c r="B121" t="s">
+        <v>26</v>
+      </c>
+      <c r="C121" t="s">
+        <v>190</v>
+      </c>
+      <c r="D121" t="s">
+        <v>28</v>
+      </c>
+      <c r="E121" t="s">
+        <v>29</v>
+      </c>
+      <c r="H121">
+        <v>0</v>
+      </c>
+      <c r="I121">
+        <v>0</v>
+      </c>
+      <c r="K121">
+        <v>160</v>
+      </c>
+      <c r="L121" t="s">
+        <v>30</v>
+      </c>
+      <c r="M121">
+        <v>0</v>
+      </c>
+      <c r="N121" t="s">
+        <v>126</v>
+      </c>
+      <c r="O121">
+        <v>0</v>
+      </c>
+      <c r="P121">
+        <v>0</v>
+      </c>
+      <c r="U121">
+        <v>0</v>
+      </c>
+      <c r="V121">
+        <v>0</v>
+      </c>
+      <c r="W121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>25</v>
+      </c>
+      <c r="B122" t="s">
+        <v>26</v>
+      </c>
+      <c r="C122" t="s">
+        <v>191</v>
+      </c>
+      <c r="D122" t="s">
+        <v>28</v>
+      </c>
+      <c r="E122" t="s">
+        <v>29</v>
+      </c>
+      <c r="H122">
+        <v>0</v>
+      </c>
+      <c r="I122">
+        <v>0</v>
+      </c>
+      <c r="K122">
+        <v>160</v>
+      </c>
+      <c r="L122" t="s">
+        <v>30</v>
+      </c>
+      <c r="M122">
+        <v>0</v>
+      </c>
+      <c r="N122" t="s">
+        <v>126</v>
+      </c>
+      <c r="O122">
+        <v>0</v>
+      </c>
+      <c r="P122">
+        <v>0</v>
+      </c>
+      <c r="U122">
+        <v>0</v>
+      </c>
+      <c r="V122">
+        <v>0</v>
+      </c>
+      <c r="W122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>25</v>
+      </c>
+      <c r="B123" t="s">
+        <v>26</v>
+      </c>
+      <c r="C123" t="s">
+        <v>192</v>
+      </c>
+      <c r="D123" t="s">
+        <v>28</v>
+      </c>
+      <c r="E123" t="s">
+        <v>29</v>
+      </c>
+      <c r="H123">
+        <v>0</v>
+      </c>
+      <c r="I123">
+        <v>0</v>
+      </c>
+      <c r="K123">
+        <v>320</v>
+      </c>
+      <c r="L123" t="s">
+        <v>30</v>
+      </c>
+      <c r="M123">
+        <v>0</v>
+      </c>
+      <c r="N123" t="s">
+        <v>126</v>
+      </c>
+      <c r="O123">
+        <v>0</v>
+      </c>
+      <c r="P123">
+        <v>0</v>
+      </c>
+      <c r="U123">
+        <v>0</v>
+      </c>
+      <c r="V123">
+        <v>0</v>
+      </c>
+      <c r="W123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>25</v>
+      </c>
+      <c r="B124" t="s">
+        <v>26</v>
+      </c>
+      <c r="C124" t="s">
+        <v>189</v>
+      </c>
+      <c r="D124" t="s">
+        <v>28</v>
+      </c>
+      <c r="E124" t="s">
+        <v>29</v>
+      </c>
+      <c r="H124">
+        <v>0</v>
+      </c>
+      <c r="I124">
+        <v>0</v>
+      </c>
+      <c r="K124">
+        <v>160</v>
+      </c>
+      <c r="L124" t="s">
+        <v>30</v>
+      </c>
+      <c r="M124">
+        <v>0</v>
+      </c>
+      <c r="N124" t="s">
+        <v>141</v>
+      </c>
+      <c r="O124">
+        <v>0</v>
+      </c>
+      <c r="P124">
+        <v>0</v>
+      </c>
+      <c r="U124">
+        <v>0</v>
+      </c>
+      <c r="V124">
+        <v>0</v>
+      </c>
+      <c r="W124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>25</v>
+      </c>
+      <c r="B125" t="s">
+        <v>26</v>
+      </c>
+      <c r="C125" t="s">
+        <v>193</v>
+      </c>
+      <c r="D125" t="s">
+        <v>38</v>
+      </c>
+      <c r="E125" t="s">
+        <v>29</v>
+      </c>
+      <c r="F125">
+        <v>167</v>
+      </c>
+      <c r="G125" t="s">
+        <v>39</v>
+      </c>
+      <c r="H125">
+        <v>4289</v>
+      </c>
+      <c r="I125">
+        <v>1.268594</v>
+      </c>
+      <c r="J125">
+        <v>25.341317369999999</v>
+      </c>
+      <c r="K125">
+        <v>160</v>
+      </c>
+      <c r="L125" t="s">
+        <v>30</v>
+      </c>
+      <c r="M125">
+        <v>4232</v>
+      </c>
+      <c r="N125" t="s">
+        <v>95</v>
+      </c>
+      <c r="O125">
+        <v>5441</v>
+      </c>
+      <c r="P125">
+        <v>777.79819899999995</v>
+      </c>
+      <c r="Q125">
+        <v>167</v>
+      </c>
+      <c r="S125">
+        <v>25.341317</v>
+      </c>
+      <c r="T125">
+        <v>3.0692889999999999</v>
+      </c>
+      <c r="U125">
+        <v>201</v>
+      </c>
+      <c r="V125">
+        <v>3.6941739999999998</v>
+      </c>
+      <c r="W125">
+        <v>21.054725999999999</v>
+      </c>
+      <c r="X125">
+        <v>141</v>
+      </c>
+      <c r="Y125">
+        <v>30.014184</v>
+      </c>
+    </row>
+    <row r="126" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>25</v>
+      </c>
+      <c r="B126" t="s">
+        <v>26</v>
+      </c>
+      <c r="C126" t="s">
+        <v>194</v>
+      </c>
+      <c r="D126" t="s">
+        <v>38</v>
+      </c>
+      <c r="E126" t="s">
+        <v>29</v>
+      </c>
+      <c r="F126">
+        <v>76</v>
+      </c>
+      <c r="G126" t="s">
+        <v>39</v>
+      </c>
+      <c r="H126">
+        <v>2804</v>
+      </c>
+      <c r="I126">
+        <v>1.6291009999999999</v>
+      </c>
+      <c r="J126">
+        <v>55.565789469999999</v>
+      </c>
+      <c r="K126">
+        <v>160</v>
+      </c>
+      <c r="L126" t="s">
+        <v>30</v>
+      </c>
+      <c r="M126">
+        <v>4223</v>
+      </c>
+      <c r="N126" t="s">
+        <v>95</v>
+      </c>
+      <c r="O126">
+        <v>4568</v>
+      </c>
+      <c r="P126">
+        <v>924.47460599999999</v>
+      </c>
+      <c r="Q126">
+        <v>76</v>
+      </c>
+      <c r="S126">
+        <v>55.565789000000002</v>
+      </c>
+      <c r="T126">
+        <v>1.663748</v>
+      </c>
+      <c r="U126">
+        <v>122</v>
+      </c>
+      <c r="V126">
+        <v>2.6707529999999999</v>
+      </c>
+      <c r="W126">
+        <v>34.614753999999998</v>
+      </c>
+      <c r="X126">
+        <v>1</v>
+      </c>
+      <c r="Y126">
+        <v>4223</v>
+      </c>
+    </row>
+    <row r="127" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>25</v>
+      </c>
+      <c r="B127" t="s">
+        <v>26</v>
+      </c>
+      <c r="C127" t="s">
+        <v>195</v>
+      </c>
+      <c r="D127" t="s">
+        <v>38</v>
+      </c>
+      <c r="E127" t="s">
+        <v>29</v>
+      </c>
+      <c r="F127">
+        <v>104</v>
+      </c>
+      <c r="G127" t="s">
+        <v>39</v>
+      </c>
+      <c r="H127">
+        <v>3196</v>
+      </c>
+      <c r="I127">
+        <v>1.270025</v>
+      </c>
+      <c r="J127">
+        <v>40.95192308</v>
+      </c>
+      <c r="K127">
+        <v>160</v>
+      </c>
+      <c r="L127" t="s">
+        <v>30</v>
+      </c>
+      <c r="M127">
+        <v>4259</v>
+      </c>
+      <c r="N127" t="s">
+        <v>95</v>
+      </c>
+      <c r="O127">
+        <v>4059</v>
+      </c>
+      <c r="P127">
+        <v>1049.27322</v>
+      </c>
+      <c r="Q127">
+        <v>104</v>
+      </c>
+      <c r="S127">
+        <v>40.951923000000001</v>
+      </c>
+      <c r="T127">
+        <v>2.5622069999999999</v>
+      </c>
+      <c r="U127">
+        <v>114</v>
+      </c>
+      <c r="V127">
+        <v>2.8085740000000001</v>
+      </c>
+      <c r="W127">
+        <v>37.359648999999997</v>
+      </c>
+      <c r="X127">
+        <v>83</v>
+      </c>
+      <c r="Y127">
+        <v>51.313253000000003</v>
+      </c>
+    </row>
+    <row r="128" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>25</v>
+      </c>
+      <c r="B128" t="s">
+        <v>26</v>
+      </c>
+      <c r="C128" t="s">
+        <v>196</v>
+      </c>
+      <c r="D128" t="s">
+        <v>38</v>
+      </c>
+      <c r="E128" t="s">
+        <v>29</v>
+      </c>
+      <c r="F128">
+        <v>134</v>
+      </c>
+      <c r="G128" t="s">
+        <v>39</v>
+      </c>
+      <c r="H128">
+        <v>4065</v>
+      </c>
+      <c r="I128">
+        <v>1.2002459999999999</v>
+      </c>
+      <c r="J128">
+        <v>31.738805970000001</v>
+      </c>
+      <c r="K128">
+        <v>160</v>
+      </c>
+      <c r="L128" t="s">
+        <v>30</v>
+      </c>
+      <c r="M128">
+        <v>4253</v>
+      </c>
+      <c r="N128" t="s">
+        <v>95</v>
+      </c>
+      <c r="O128">
+        <v>4879</v>
+      </c>
+      <c r="P128">
+        <v>871.695019</v>
+      </c>
+      <c r="Q128">
+        <v>134</v>
+      </c>
+      <c r="S128">
+        <v>31.738806</v>
+      </c>
+      <c r="T128">
+        <v>2.746464</v>
+      </c>
+      <c r="U128">
+        <v>142</v>
+      </c>
+      <c r="V128">
+        <v>2.9104320000000001</v>
+      </c>
+      <c r="W128">
+        <v>29.950704000000002</v>
+      </c>
+      <c r="X128">
+        <v>104</v>
+      </c>
+      <c r="Y128">
+        <v>40.894230999999998</v>
+      </c>
+    </row>
+    <row r="129" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>25</v>
+      </c>
+      <c r="B129" t="s">
+        <v>26</v>
+      </c>
+      <c r="C129" t="s">
+        <v>197</v>
+      </c>
+      <c r="D129" t="s">
+        <v>38</v>
+      </c>
+      <c r="E129" t="s">
+        <v>29</v>
+      </c>
+      <c r="F129">
+        <v>195</v>
+      </c>
+      <c r="G129" t="s">
+        <v>39</v>
+      </c>
+      <c r="H129">
+        <v>2534</v>
+      </c>
+      <c r="I129">
+        <v>1.4198900000000001</v>
+      </c>
+      <c r="J129">
+        <v>21.74871795</v>
+      </c>
+      <c r="K129">
+        <v>160</v>
+      </c>
+      <c r="L129" t="s">
+        <v>30</v>
+      </c>
+      <c r="M129">
+        <v>4241</v>
+      </c>
+      <c r="N129" t="s">
+        <v>95</v>
+      </c>
+      <c r="O129">
+        <v>3598</v>
+      </c>
+      <c r="P129">
+        <v>1178.7103950000001</v>
+      </c>
+      <c r="Q129">
+        <v>195</v>
+      </c>
+      <c r="S129">
+        <v>21.748718</v>
+      </c>
+      <c r="T129">
+        <v>5.4196780000000002</v>
+      </c>
+      <c r="U129">
+        <v>220</v>
+      </c>
+      <c r="V129">
+        <v>6.1145079999999998</v>
+      </c>
+      <c r="W129">
+        <v>19.277273000000001</v>
+      </c>
+      <c r="X129">
+        <v>6</v>
+      </c>
+      <c r="Y129">
+        <v>706.83333300000004</v>
+      </c>
+    </row>
+    <row r="130" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>25</v>
+      </c>
+      <c r="B130" t="s">
+        <v>26</v>
+      </c>
+      <c r="C130" t="s">
+        <v>198</v>
+      </c>
+      <c r="D130" t="s">
+        <v>38</v>
+      </c>
+      <c r="E130" t="s">
+        <v>29</v>
+      </c>
+      <c r="F130">
+        <v>157</v>
+      </c>
+      <c r="G130" t="s">
+        <v>39</v>
+      </c>
+      <c r="H130">
+        <v>4147</v>
+      </c>
+      <c r="I130">
+        <v>1.234869</v>
+      </c>
+      <c r="J130">
+        <v>26.993630570000001</v>
+      </c>
+      <c r="K130">
+        <v>160</v>
+      </c>
+      <c r="L130" t="s">
+        <v>30</v>
+      </c>
+      <c r="M130">
+        <v>4238</v>
+      </c>
+      <c r="N130" t="s">
+        <v>95</v>
+      </c>
+      <c r="O130">
+        <v>5121</v>
+      </c>
+      <c r="P130">
+        <v>827.57273999999995</v>
+      </c>
+      <c r="Q130">
+        <v>157</v>
+      </c>
+      <c r="S130">
+        <v>26.993631000000001</v>
+      </c>
+      <c r="T130">
+        <v>3.0658069999999999</v>
+      </c>
+      <c r="U130">
+        <v>170</v>
+      </c>
+      <c r="V130">
+        <v>3.3196639999999999</v>
+      </c>
+      <c r="W130">
+        <v>24.929411999999999</v>
+      </c>
+      <c r="X130">
+        <v>139</v>
+      </c>
+      <c r="Y130">
+        <v>30.489208999999999</v>
+      </c>
+    </row>
+    <row r="131" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>25</v>
+      </c>
+      <c r="B131" t="s">
+        <v>26</v>
+      </c>
+      <c r="C131" t="s">
+        <v>199</v>
+      </c>
+      <c r="D131" t="s">
+        <v>38</v>
+      </c>
+      <c r="E131" t="s">
+        <v>29</v>
+      </c>
+      <c r="F131">
+        <v>229</v>
+      </c>
+      <c r="G131" t="s">
+        <v>39</v>
+      </c>
+      <c r="H131">
+        <v>5084</v>
+      </c>
+      <c r="I131">
+        <v>1.2759640000000001</v>
+      </c>
+      <c r="J131">
+        <v>18.40611354</v>
+      </c>
+      <c r="K131">
+        <v>160</v>
+      </c>
+      <c r="L131" t="s">
+        <v>30</v>
+      </c>
+      <c r="M131">
+        <v>4215</v>
+      </c>
+      <c r="N131" t="s">
+        <v>95</v>
+      </c>
+      <c r="O131">
+        <v>6487</v>
+      </c>
+      <c r="P131">
+        <v>649.76106100000004</v>
+      </c>
+      <c r="Q131">
+        <v>229</v>
+      </c>
+      <c r="S131">
+        <v>18.406113999999999</v>
+      </c>
+      <c r="T131">
+        <v>3.5301369999999999</v>
+      </c>
+      <c r="U131">
+        <v>263</v>
+      </c>
+      <c r="V131">
+        <v>4.0542619999999996</v>
+      </c>
+      <c r="W131">
+        <v>16.026616000000001</v>
+      </c>
+      <c r="X131">
+        <v>174</v>
+      </c>
+      <c r="Y131">
+        <v>24.224138</v>
+      </c>
+    </row>
+    <row r="132" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>25</v>
+      </c>
+      <c r="B132" t="s">
+        <v>26</v>
+      </c>
+      <c r="C132" t="s">
+        <v>200</v>
+      </c>
+      <c r="D132" t="s">
+        <v>38</v>
+      </c>
+      <c r="E132" t="s">
+        <v>29</v>
+      </c>
+      <c r="F132">
+        <v>184</v>
+      </c>
+      <c r="G132" t="s">
+        <v>39</v>
+      </c>
+      <c r="H132">
+        <v>5048</v>
+      </c>
+      <c r="I132">
+        <v>1.3229</v>
+      </c>
+      <c r="J132">
+        <v>22.913043479999999</v>
+      </c>
+      <c r="K132">
+        <v>160</v>
+      </c>
+      <c r="L132" t="s">
+        <v>30</v>
+      </c>
+      <c r="M132">
+        <v>4216</v>
+      </c>
+      <c r="N132" t="s">
+        <v>95</v>
+      </c>
+      <c r="O132">
+        <v>6678</v>
+      </c>
+      <c r="P132">
+        <v>631.32674499999996</v>
+      </c>
+      <c r="Q132">
+        <v>184</v>
+      </c>
+      <c r="S132">
+        <v>22.913042999999998</v>
+      </c>
+      <c r="T132">
+        <v>2.7553160000000001</v>
+      </c>
+      <c r="U132">
+        <v>224</v>
+      </c>
+      <c r="V132">
+        <v>3.354298</v>
+      </c>
+      <c r="W132">
+        <v>18.821428999999998</v>
+      </c>
+      <c r="X132">
+        <v>150</v>
+      </c>
+      <c r="Y132">
+        <v>28.106667000000002</v>
+      </c>
+    </row>
+    <row r="133" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>25</v>
+      </c>
+      <c r="B133" t="s">
+        <v>26</v>
+      </c>
+      <c r="C133" t="s">
+        <v>201</v>
+      </c>
+      <c r="D133" t="s">
+        <v>28</v>
+      </c>
+      <c r="E133" t="s">
+        <v>29</v>
+      </c>
+      <c r="F133">
+        <v>93</v>
+      </c>
+      <c r="G133" t="s">
+        <v>39</v>
+      </c>
+      <c r="H133">
+        <v>2107</v>
+      </c>
+      <c r="I133">
+        <v>1.5158990000000001</v>
+      </c>
+      <c r="J133">
+        <v>44.064516130000001</v>
+      </c>
+      <c r="K133">
+        <v>160</v>
+      </c>
+      <c r="L133" t="s">
+        <v>30</v>
+      </c>
+      <c r="M133">
+        <v>4098</v>
+      </c>
+      <c r="N133" t="s">
+        <v>202</v>
+      </c>
+      <c r="O133">
+        <v>3194</v>
+      </c>
+      <c r="P133">
+        <v>1283.030683</v>
+      </c>
+      <c r="Q133">
+        <v>93</v>
+      </c>
+      <c r="S133">
+        <v>44.064515999999998</v>
+      </c>
+      <c r="T133">
+        <v>2.9117090000000001</v>
+      </c>
+      <c r="U133">
+        <v>103</v>
+      </c>
+      <c r="V133">
+        <v>3.224796</v>
+      </c>
+      <c r="W133">
+        <v>39.786408000000002</v>
+      </c>
+      <c r="X133">
+        <v>74</v>
+      </c>
+      <c r="Y133">
+        <v>55.378377999999998</v>
+      </c>
+    </row>
+    <row r="134" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>25</v>
+      </c>
+      <c r="B134" t="s">
+        <v>26</v>
+      </c>
+      <c r="C134" t="s">
+        <v>203</v>
+      </c>
+      <c r="D134" t="s">
+        <v>38</v>
+      </c>
+      <c r="E134" t="s">
+        <v>29</v>
+      </c>
+      <c r="H134">
+        <v>0</v>
+      </c>
+      <c r="I134">
+        <v>0</v>
+      </c>
+      <c r="K134">
+        <v>160</v>
+      </c>
+      <c r="L134" t="s">
+        <v>30</v>
+      </c>
+      <c r="M134">
+        <v>0</v>
+      </c>
+      <c r="N134" t="s">
+        <v>204</v>
+      </c>
+      <c r="O134">
+        <v>0</v>
+      </c>
+      <c r="P134">
+        <v>0</v>
+      </c>
+      <c r="U134">
+        <v>0</v>
+      </c>
+      <c r="V134">
+        <v>0</v>
+      </c>
+      <c r="W134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>25</v>
+      </c>
+      <c r="B135" t="s">
+        <v>26</v>
+      </c>
+      <c r="C135" t="s">
+        <v>205</v>
+      </c>
+      <c r="D135" t="s">
+        <v>38</v>
+      </c>
+      <c r="E135" t="s">
+        <v>29</v>
+      </c>
+      <c r="H135">
+        <v>0</v>
+      </c>
+      <c r="I135">
+        <v>0</v>
+      </c>
+      <c r="K135">
+        <v>160</v>
+      </c>
+      <c r="L135" t="s">
+        <v>30</v>
+      </c>
+      <c r="M135">
+        <v>0</v>
+      </c>
+      <c r="N135" t="s">
+        <v>204</v>
+      </c>
+      <c r="O135">
+        <v>0</v>
+      </c>
+      <c r="P135">
+        <v>0</v>
+      </c>
+      <c r="U135">
+        <v>0</v>
+      </c>
+      <c r="V135">
+        <v>0</v>
+      </c>
+      <c r="W135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>25</v>
+      </c>
+      <c r="B136" t="s">
+        <v>26</v>
+      </c>
+      <c r="C136" t="s">
+        <v>206</v>
+      </c>
+      <c r="D136" t="s">
+        <v>38</v>
+      </c>
+      <c r="E136" t="s">
+        <v>29</v>
+      </c>
+      <c r="H136">
+        <v>0</v>
+      </c>
+      <c r="I136">
+        <v>0</v>
+      </c>
+      <c r="K136">
+        <v>160</v>
+      </c>
+      <c r="L136" t="s">
+        <v>30</v>
+      </c>
+      <c r="M136">
+        <v>0</v>
+      </c>
+      <c r="N136" t="s">
+        <v>204</v>
+      </c>
+      <c r="O136">
+        <v>0</v>
+      </c>
+      <c r="P136">
+        <v>0</v>
+      </c>
+      <c r="U136">
+        <v>0</v>
+      </c>
+      <c r="V136">
+        <v>0</v>
+      </c>
+      <c r="W136">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>25</v>
+      </c>
+      <c r="B137" t="s">
+        <v>26</v>
+      </c>
+      <c r="C137" t="s">
+        <v>207</v>
+      </c>
+      <c r="D137" t="s">
+        <v>38</v>
+      </c>
+      <c r="E137" t="s">
+        <v>29</v>
+      </c>
+      <c r="H137">
+        <v>0</v>
+      </c>
+      <c r="I137">
+        <v>0</v>
+      </c>
+      <c r="K137">
+        <v>160</v>
+      </c>
+      <c r="L137" t="s">
+        <v>30</v>
+      </c>
+      <c r="M137">
+        <v>0</v>
+      </c>
+      <c r="N137" t="s">
+        <v>204</v>
+      </c>
+      <c r="O137">
+        <v>0</v>
+      </c>
+      <c r="P137">
+        <v>0</v>
+      </c>
+      <c r="U137">
+        <v>0</v>
+      </c>
+      <c r="V137">
+        <v>0</v>
+      </c>
+      <c r="W137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>25</v>
+      </c>
+      <c r="B138" t="s">
+        <v>26</v>
+      </c>
+      <c r="C138" t="s">
+        <v>208</v>
+      </c>
+      <c r="D138" t="s">
+        <v>38</v>
+      </c>
+      <c r="E138" t="s">
+        <v>29</v>
+      </c>
+      <c r="H138">
+        <v>0</v>
+      </c>
+      <c r="I138">
+        <v>0</v>
+      </c>
+      <c r="K138">
+        <v>160</v>
+      </c>
+      <c r="L138" t="s">
+        <v>30</v>
+      </c>
+      <c r="M138">
+        <v>0</v>
+      </c>
+      <c r="N138" t="s">
+        <v>204</v>
+      </c>
+      <c r="O138">
+        <v>0</v>
+      </c>
+      <c r="P138">
+        <v>0</v>
+      </c>
+      <c r="U138">
+        <v>0</v>
+      </c>
+      <c r="V138">
+        <v>0</v>
+      </c>
+      <c r="W138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>25</v>
+      </c>
+      <c r="B139" t="s">
+        <v>26</v>
+      </c>
+      <c r="C139" t="s">
+        <v>209</v>
+      </c>
+      <c r="D139" t="s">
+        <v>38</v>
+      </c>
+      <c r="E139" t="s">
+        <v>29</v>
+      </c>
+      <c r="H139">
+        <v>0</v>
+      </c>
+      <c r="I139">
+        <v>0</v>
+      </c>
+      <c r="K139">
+        <v>160</v>
+      </c>
+      <c r="L139" t="s">
+        <v>30</v>
+      </c>
+      <c r="M139">
+        <v>0</v>
+      </c>
+      <c r="N139" t="s">
+        <v>204</v>
+      </c>
+      <c r="O139">
+        <v>0</v>
+      </c>
+      <c r="P139">
+        <v>0</v>
+      </c>
+      <c r="U139">
+        <v>0</v>
+      </c>
+      <c r="V139">
+        <v>0</v>
+      </c>
+      <c r="W139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>25</v>
+      </c>
+      <c r="B140" t="s">
+        <v>26</v>
+      </c>
+      <c r="C140" t="s">
+        <v>210</v>
+      </c>
+      <c r="D140" t="s">
+        <v>38</v>
+      </c>
+      <c r="E140" t="s">
+        <v>29</v>
+      </c>
+      <c r="H140">
+        <v>0</v>
+      </c>
+      <c r="I140">
+        <v>0</v>
+      </c>
+      <c r="K140">
+        <v>160</v>
+      </c>
+      <c r="L140" t="s">
+        <v>30</v>
+      </c>
+      <c r="M140">
+        <v>0</v>
+      </c>
+      <c r="N140" t="s">
+        <v>204</v>
+      </c>
+      <c r="O140">
+        <v>0</v>
+      </c>
+      <c r="P140">
+        <v>0</v>
+      </c>
+      <c r="U140">
+        <v>0</v>
+      </c>
+      <c r="V140">
+        <v>0</v>
+      </c>
+      <c r="W140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>25</v>
+      </c>
+      <c r="B141" t="s">
+        <v>26</v>
+      </c>
+      <c r="C141" t="s">
+        <v>211</v>
+      </c>
+      <c r="D141" t="s">
+        <v>38</v>
+      </c>
+      <c r="E141" t="s">
+        <v>29</v>
+      </c>
+      <c r="H141">
+        <v>0</v>
+      </c>
+      <c r="I141">
+        <v>0</v>
+      </c>
+      <c r="K141">
+        <v>160</v>
+      </c>
+      <c r="L141" t="s">
+        <v>30</v>
+      </c>
+      <c r="M141">
+        <v>0</v>
+      </c>
+      <c r="N141" t="s">
+        <v>204</v>
+      </c>
+      <c r="O141">
+        <v>0</v>
+      </c>
+      <c r="P141">
+        <v>0</v>
+      </c>
+      <c r="U141">
+        <v>0</v>
+      </c>
+      <c r="V141">
+        <v>0</v>
+      </c>
+      <c r="W141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>25</v>
+      </c>
+      <c r="B142" t="s">
+        <v>26</v>
+      </c>
+      <c r="C142" t="s">
+        <v>212</v>
+      </c>
+      <c r="D142" t="s">
+        <v>28</v>
+      </c>
+      <c r="E142" t="s">
+        <v>29</v>
+      </c>
+      <c r="H142">
+        <v>0</v>
+      </c>
+      <c r="I142">
+        <v>0</v>
+      </c>
+      <c r="K142">
+        <v>160</v>
+      </c>
+      <c r="L142" t="s">
+        <v>30</v>
+      </c>
+      <c r="M142">
+        <v>0</v>
+      </c>
+      <c r="N142" t="s">
+        <v>204</v>
+      </c>
+      <c r="O142">
+        <v>0</v>
+      </c>
+      <c r="P142">
+        <v>0</v>
+      </c>
+      <c r="U142">
+        <v>0</v>
+      </c>
+      <c r="V142">
+        <v>0</v>
+      </c>
+      <c r="W142">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
